--- a/naver-place-crawler/results_health/강북_PT.xlsx
+++ b/naver-place-crawler/results_health/강북_PT.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
     <col width="47" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q2" t="n">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="R2" t="n">
         <v>813</v>
@@ -646,41 +646,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>데일리PT샵 미아본점</t>
+          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dailypt0926@naver.com</t>
+          <t>dwgym1@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1362-0934</t>
+          <t>0507-1370-7849</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98</t>
+          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dailypt0926</t>
+          <t>https://blog.naver.com/dwgym1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>78</v>
+        <v>2657</v>
       </c>
       <c r="Q3" t="n">
-        <v>1250</v>
+        <v>4788</v>
       </c>
       <c r="R3" t="n">
-        <v>1328</v>
+        <v>7445</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +730,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1069239956</t>
+          <t>1284235115</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069239956</t>
+          <t>https://m.place.naver.com/place/1284235115</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+          <t>데일리PT샵 미아본점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dwgym1@naver.com</t>
+          <t>dailypt0926@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1370-7849</t>
+          <t>0507-1362-0934</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
+          <t>서울특별시 강북구 도봉로 98</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dwgym1</t>
+          <t>https://blog.naver.com/dailypt0926</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2649</v>
+        <v>78</v>
       </c>
       <c r="Q4" t="n">
-        <v>4706</v>
+        <v>1295</v>
       </c>
       <c r="R4" t="n">
-        <v>7355</v>
+        <v>1373</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1284235115</t>
+          <t>1069239956</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284235115</t>
+          <t>https://m.place.naver.com/place/1069239956</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -846,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>버클필라테스&amp;PT 미아점</t>
+          <t>라이프빌딩PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>buckle1234@naver.com</t>
+          <t>life_building_@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1485-1323</t>
+          <t>0507-1404-1363</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
+          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_YLwxfn/chat</t>
+          <t>https://www.instagram.com/lifebuildingpt/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -894,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>636</v>
+        <v>532</v>
       </c>
       <c r="Q5" t="n">
-        <v>696</v>
+        <v>2236</v>
       </c>
       <c r="R5" t="n">
-        <v>1332</v>
+        <v>2768</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +918,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1358291633</t>
+          <t>1906517072</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358291633</t>
+          <t>https://m.place.naver.com/place/1906517072</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포애니 수유역점</t>
+          <t>짐코사트 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spoany52@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1310-9628</t>
+          <t>0507-1308-4535</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
+          <t>서울특별시 강북구 수유로 81 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany52</t>
+          <t>https://blog.naver.com/97_cosat</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2723</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2327</v>
+        <v>154</v>
       </c>
       <c r="R6" t="n">
-        <v>5050</v>
+        <v>179</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1440007035</t>
+          <t>1604797933</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1440007035</t>
+          <t>https://m.place.naver.com/place/1604797933</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4535</v>
+        <v>4545</v>
       </c>
       <c r="Q7" t="n">
-        <v>1324</v>
+        <v>1203</v>
       </c>
       <c r="R7" t="n">
-        <v>5859</v>
+        <v>5748</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/강북_PT.xlsx
+++ b/naver-place-crawler/results_health/강북_PT.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="47" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -624,10 +624,10 @@
         <v>230</v>
       </c>
       <c r="Q2" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="R2" t="n">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,41 +646,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+          <t>짐코사트 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dwgym1@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1370-7849</t>
+          <t>0507-1308-4535</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
+          <t>서울특별시 강북구 수유로 81 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dwgym1</t>
+          <t>https://blog.naver.com/97_cosat</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2657</v>
+        <v>24</v>
       </c>
       <c r="Q3" t="n">
-        <v>4788</v>
+        <v>157</v>
       </c>
       <c r="R3" t="n">
-        <v>7445</v>
+        <v>181</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +730,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1284235115</t>
+          <t>1604797933</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284235115</t>
+          <t>https://m.place.naver.com/place/1604797933</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>데일리PT샵 미아본점</t>
+          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dailypt0926@naver.com</t>
+          <t>dwgym1@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1362-0934</t>
+          <t>0507-1370-7849</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98</t>
+          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dailypt0926</t>
+          <t>https://blog.naver.com/dwgym1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>78</v>
+        <v>2661</v>
       </c>
       <c r="Q4" t="n">
-        <v>1295</v>
+        <v>4788</v>
       </c>
       <c r="R4" t="n">
-        <v>1373</v>
+        <v>7449</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1069239956</t>
+          <t>1284235115</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069239956</t>
+          <t>https://m.place.naver.com/place/1284235115</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>라이프빌딩PT</t>
+          <t>데일리PT샵 미아본점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>life_building_@naver.com</t>
+          <t>dailypt0926@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1404-1363</t>
+          <t>0507-1362-0934</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
+          <t>서울특별시 강북구 도봉로 98</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifebuildingpt/</t>
+          <t>https://blog.naver.com/dailypt0926</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>532</v>
+        <v>78</v>
       </c>
       <c r="Q5" t="n">
-        <v>2236</v>
+        <v>1300</v>
       </c>
       <c r="R5" t="n">
-        <v>2768</v>
+        <v>1378</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +918,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1906517072</t>
+          <t>1069239956</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1906517072</t>
+          <t>https://m.place.naver.com/place/1069239956</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>짐코사트 헬스&amp;PT 수유점</t>
+          <t>레디포짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>ready4gymsuyu@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1308-4535</t>
+          <t>0507-1430-3344</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유로 81 3층</t>
+          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>https://blog.naver.com/ready4gymsuyu</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>25</v>
+        <v>1086</v>
       </c>
       <c r="Q6" t="n">
-        <v>154</v>
+        <v>864</v>
       </c>
       <c r="R6" t="n">
-        <v>179</v>
+        <v>1950</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1604797933</t>
+          <t>38648497</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604797933</t>
+          <t>https://m.place.naver.com/place/38648497</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4545</v>
+        <v>4547</v>
       </c>
       <c r="Q7" t="n">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="R7" t="n">
-        <v>5748</v>
+        <v>5751</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/강북_PT.xlsx
+++ b/naver-place-crawler/results_health/강북_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
+          <t>파인드미짐 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>uphoria6825@naver.com</t>
+          <t>find_me_pt_studio@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1334-6825</t>
+          <t>0507-1478-5103</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
+          <t>서울특별시 강북구 한천로144길 11 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uphoria_mia_1/</t>
+          <t>https://blog.naver.com/find_me_pt_studio</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="Q2" t="n">
-        <v>584</v>
+        <v>423</v>
       </c>
       <c r="R2" t="n">
-        <v>814</v>
+        <v>649</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1037773645</t>
+          <t>1116831923</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037773645</t>
+          <t>https://m.place.naver.com/place/1116831923</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,39 +653,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>짐코사트 헬스&amp;PT 수유점</t>
+          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>lifebuildingmia@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1308-4535</t>
+          <t>0507-1332-1672</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유로 81 3층</t>
+          <t>서울특별시 강북구 도봉로 136 9층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>https://landing-mia-ebon.vercel.app/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>24</v>
+        <v>321</v>
       </c>
       <c r="Q3" t="n">
-        <v>157</v>
+        <v>580</v>
       </c>
       <c r="R3" t="n">
-        <v>181</v>
+        <v>901</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1604797933</t>
+          <t>36362933</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604797933</t>
+          <t>https://m.place.naver.com/place/36362933</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+          <t>트렌디우먼휘트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dwgym1@naver.com</t>
+          <t>trend_hd4@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1370-7849</t>
+          <t>02-988-3124</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
+          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dwgym1</t>
+          <t>https://blog.naver.com/trend_hd4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2661</v>
+        <v>2264</v>
       </c>
       <c r="Q4" t="n">
-        <v>4788</v>
+        <v>1432</v>
       </c>
       <c r="R4" t="n">
-        <v>7449</v>
+        <v>3696</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1284235115</t>
+          <t>1885902314</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284235115</t>
+          <t>https://m.place.naver.com/place/1885902314</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>데일리PT샵 미아본점</t>
+          <t>데일리프리미엄 그룹PT샵 미아점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dailypt0926@naver.com</t>
+          <t>dailygrouppt@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1362-0934</t>
+          <t>0507-1385-0454</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98</t>
+          <t>서울특별시 강북구 도봉로 98 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dailypt0926</t>
+          <t>https://www.instagram.com/luv.dailypt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="Q5" t="n">
-        <v>1300</v>
+        <v>64</v>
       </c>
       <c r="R5" t="n">
-        <v>1378</v>
+        <v>107</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1069239956</t>
+          <t>2069382925</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069239956</t>
+          <t>https://m.place.naver.com/place/2069382925</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,39 +940,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>레디포짐 헬스&amp;PT 수유점</t>
+          <t>하이엔드짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ready4gymsuyu@naver.com</t>
+          <t>highend_fit@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1430-3344</t>
+          <t>0507-1417-2362</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
+          <t>서울특별시 강북구 한천로 1035 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ready4gymsuyu</t>
+          <t>https://highendgymsuyu-landing.vercel.app</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1086</v>
+        <v>1811</v>
       </c>
       <c r="Q6" t="n">
-        <v>864</v>
+        <v>1185</v>
       </c>
       <c r="R6" t="n">
-        <v>1950</v>
+        <v>2996</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>38648497</t>
+          <t>1953510990</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38648497</t>
+          <t>https://m.place.naver.com/place/1953510990</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,34 +1034,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>에이블짐 수유점</t>
+          <t>짐박스피트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ablegym33@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1340-7281</t>
+          <t>0507-1391-2161</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
+          <t>서울특별시 강북구 도봉로 52</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym33/223928936059</t>
+          <t>https://gymboxx.com/onceinayear?gym=79</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1082,7 +1086,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,30 +1095,7898 @@
         </is>
       </c>
       <c r="P7" t="n">
+        <v>1139</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>41</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1180</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2099546838</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2099546838</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>에스핏 휘트니스 수유점</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>kdhonepick@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1393-8101</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로67길 18 3층</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kdhonepick</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>243</v>
+      </c>
+      <c r="R8" t="n">
+        <v>359</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1185739926</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1185739926</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>rkdqnr7184@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1336-7184</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_QERxeG</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>462</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>795</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1257</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1172555749</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1172555749</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>osbum0224@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>02-986-2534</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>http://www.thebarunfitness.com</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>104</v>
+      </c>
+      <c r="R10" t="n">
+        <v>184</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>38636716</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38636716</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>스포애니 삼양사거리점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>spoany87@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1338-9618</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spoany87</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>1463</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1726</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3189</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1790576623</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1790576623</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>프레스짐 헬스 &amp; PT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>codelegend@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1344-9688</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pressgym___</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>234</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>45</v>
+      </c>
+      <c r="R12" t="n">
+        <v>279</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1695685266</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1695685266</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>빌리프짐 수유점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>beliefgym4@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1343-9679</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beliefgym_suyu/</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>1620</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1195</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2815</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1058492468</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1058492468</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>070-8024-0813</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 수유동</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1662868565</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1662868565</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>이성현퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>sunghyunle2@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1437-5900</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sunghyunle2</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>29</v>
+      </c>
+      <c r="R15" t="n">
+        <v>61</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>35384521</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35384521</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>더 퍼스트짐</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ssdaw1234@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1353-7541</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로131길 29 3층</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ssdaw1234</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>93</v>
+      </c>
+      <c r="R16" t="n">
+        <v>117</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1176777711</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1176777711</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>애드TOP</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>govlfox@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>070-8227-7372</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 166</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>30824060</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/30824060</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>에이블짐 수유점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ablegym33@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1340-7281</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ablegym33/223928936059</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
         <v>4547</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q18" t="n">
         <v>1204</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R18" t="n">
         <v>5751</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
         <is>
           <t>1745960523</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1745960523</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>존버짐 미아뉴타운점</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>jonbergym3@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1368-4511</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jonbergym3</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>220</v>
+      </c>
+      <c r="R19" t="n">
+        <v>298</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1293414126</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1293414126</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>크로스핏 알앤엘 수유</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>crossfitrnl_su@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1382-4849</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 덕릉로 76 B1</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/runandlift</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>193</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>501</v>
+      </c>
+      <c r="R20" t="n">
+        <v>694</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>31777480</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31777480</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>엑시스피티</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>axis_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1339-8603</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로8길 33 2층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/axis_pt</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>44</v>
+      </c>
+      <c r="R21" t="n">
+        <v>69</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2055534881</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2055534881</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>스포애니 수유역점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>spoany52@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1310-9628</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spoany52</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>2746</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2339</v>
+      </c>
+      <c r="R22" t="n">
+        <v>5085</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1440007035</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1440007035</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>에너메카휘트니스 미아사거리점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>nyh314@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1320-7744</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enermeca2/</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>1331</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>885</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2216</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1756863852</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1756863852</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>소울휘트니스</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h9a1n94@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>02-985-5553</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/h9a1n94</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>335</v>
+      </c>
+      <c r="R24" t="n">
+        <v>450</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>37240884</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37240884</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>장소대여</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>메노모쏘</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>nana_1982@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1375-4415</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로173길 21-6 1층</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1344980412</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1344980412</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>포레스트PT짐</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>forestgym24@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/forestgym24/223778254580</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>7</v>
+      </c>
+      <c r="R26" t="n">
+        <v>28</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1008319723</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1008319723</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>프리원핏 미아점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>uckyfycmko336@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1380-1962</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/freewantfit__mia/</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>94</v>
+      </c>
+      <c r="R27" t="n">
+        <v>169</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2037364243</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2037364243</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>가설자재비티아시바피티아시바발안전난간대판매임대설치</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>rodtmdu12@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>070-8083-6616</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 수유동</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1740427970</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1740427970</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>플로리다휘트니스 삼양동점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>sd670@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1417-9917</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sd670</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>235</v>
+      </c>
+      <c r="R29" t="n">
+        <v>322</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>33937785</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33937785</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>바디채널 광산사거리점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>bodyfit_@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1359-6850</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bodychannel_kwangsan/?hl=ko</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>320</v>
+      </c>
+      <c r="R30" t="n">
+        <v>423</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1089484623</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1089484623</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>짐초이 헬스&amp;PT 수유역점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>gymchoi@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1321-8296</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gymchoi</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>347</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>347</v>
+      </c>
+      <c r="R31" t="n">
+        <v>694</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1548872331</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1548872331</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>데일리PT샵 미아본점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>dailypt0926@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1362-0934</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 98</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dailypt0926</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1300</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1378</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1069239956</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1069239956</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>통증&amp;교정연구소</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>xtmxjax@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1318-2087</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로77길 6 910호</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/xtmxjax</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>10</v>
+      </c>
+      <c r="R33" t="n">
+        <v>43</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1975301409</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1975301409</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>가설재비티아시바피티아시바파이프유로폼임대대여설치</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>rodtmdu12@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>070-8069-0778</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 미아동</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1022266242</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1022266242</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>가설재비티아시바피티아시바파이프유로폼임대대여설치</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>rodtmdu12@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>070-8069-0779</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 번동</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1752172206</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1752172206</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>노블휘트니스</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>noble_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1421-2221</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/noble_fitness</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>130</v>
+      </c>
+      <c r="R36" t="n">
+        <v>305</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>36246823</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36246823</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>블랙핏pt샵 미아사거리점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>blackfit123@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1309-1030</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/blackfit123</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>375</v>
+      </c>
+      <c r="R37" t="n">
+        <v>521</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1105932712</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1105932712</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>goodfit9008@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goodfit9008</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>247</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1343</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1590</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1850055844</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1850055844</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>레디포짐 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ready4gymsuyu@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1430-3344</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ready4gymsuyu</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>1086</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>865</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1951</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>38648497</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38648497</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>버클필라테스&amp;PT 미아점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>buckle1234@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1485-1323</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_YLwxfn/chat</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>637</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>699</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1336</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1358291633</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1358291633</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>위핏헬스&amp;PT 수유역점</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>wefit100@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1490-2127</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로139길 42 4층</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_ZWKxjn</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>821</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>559</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1380</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1661637243</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1661637243</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>라인짐휘트니스</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>linegym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1418-7007</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/linegym_</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>297</v>
+      </c>
+      <c r="R42" t="n">
+        <v>392</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>17944349</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/17944349</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>체력단련,운동</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>DL 운동센터</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>gunwigun_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔매로22가길 11 2층 201호</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://litt.ly/d.l.trainer</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1479834103</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1479834103</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>밀리언짐 수유점</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>milliongym-suyu@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1357-9092</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/milliongym-suyu</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>47</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2061019894</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2061019894</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>피티아시바</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>unixgaseol7@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>070-5255-1240</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 미아동</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1012926496</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1012926496</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>uphoria6825@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1334-6825</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/uphoria_mia_1/</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>584</v>
+      </c>
+      <c r="R46" t="n">
+        <v>814</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1037773645</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1037773645</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>에너메카 휘트니스 미아점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>nyh314@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1344-1650</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nyh314</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>334</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>365</v>
+      </c>
+      <c r="R47" t="n">
+        <v>699</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>37615690</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37615690</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>엘투휘트니스 수유번동점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>lhj0709_@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1369-2202</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>11</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2045876824</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2045876824</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>수유 재활운동센터 라이프리턴</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>lifereturn_suyu@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1377-5126</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_ExmdAX</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>54</v>
+      </c>
+      <c r="R49" t="n">
+        <v>76</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2013060255</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2013060255</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>건짐 수유역점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>gungympt@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1459-7599</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 노해로 1 지하1층</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gungympt</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>426</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>221</v>
+      </c>
+      <c r="R50" t="n">
+        <v>647</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1381178715</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1381178715</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>짐코사트 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>97_cosat@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1308-4535</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 수유로 81 3층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/97_cosat</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>157</v>
+      </c>
+      <c r="R51" t="n">
+        <v>181</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1604797933</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1604797933</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>올레이디짐 가오리점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>hyomin_nase@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1369-0010</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 416 2층</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://allladygym.imweb.me/</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>165</v>
+      </c>
+      <c r="R52" t="n">
+        <v>244</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1633562526</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1633562526</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>dwgym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1370-7849</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dwgym1</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>2659</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>4788</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7447</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1284235115</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1284235115</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>피트니스 베네핏 수유역점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>baekyuri802@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1351-2438</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/baekyuri802</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>622</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>339</v>
+      </c>
+      <c r="R54" t="n">
+        <v>961</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1550724103</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1550724103</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>wellcare093@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1404-1390</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wellcare093</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>53</v>
+      </c>
+      <c r="R55" t="n">
+        <v>61</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2039688284</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2039688284</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>제이핏 여성전용피티샵</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>lhj0709_@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>02-982-7707</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 188 5층</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jjfit_7707</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>10</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>804545907</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/804545907</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>서울가설재BT비티아시바PT피티아시바파이프비계임대시공판매</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>070-8075-1025</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 미아동</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2</v>
+      </c>
+      <c r="R57" t="n">
+        <v>2</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1003986024</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1003986024</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>우주짐 미아점 PT &amp; 헬스</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>woojoogym@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1354-5063</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 173 지층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://litt.ly/woojoogym</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>351</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>616</v>
+      </c>
+      <c r="R58" t="n">
+        <v>967</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1022408622</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1022408622</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>서울가설재BT비티아시바PT피티아시바파이프비계임대시공판매</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>070-8075-1072</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 번동</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2</v>
+      </c>
+      <c r="R59" t="n">
+        <v>2</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1764669223</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1764669223</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>더블플러스휘트니스클럽</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>osbum0224@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1306-3451</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 인수봉로 293 2층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>6</v>
+      </c>
+      <c r="R60" t="n">
+        <v>13</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1035955167</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1035955167</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>핏의공식</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>gymseungeun@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1458-1884</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로131길 17 4층</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gymseungeun/</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>47</v>
+      </c>
+      <c r="R61" t="n">
+        <v>76</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>2024627135</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2024627135</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>드림유어바디 필라테스 미아점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>popleedon@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로15길 11 3,4층 (드림유어바디)</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dyb_pilates/</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>1264</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>239</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1503</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>11630404</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11630404</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>woojoogym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1362-5063</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/woojoo_gym2/</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>218</v>
+      </c>
+      <c r="R63" t="n">
+        <v>343</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>2089127568</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2089127568</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>판타스틱짐 수유점 여성전용피트니스</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>blueskirt0704@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1338-1501</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/blueskirt0704</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>507</v>
+      </c>
+      <c r="R64" t="n">
+        <v>649</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1914282686</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1914282686</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>디와이비퍼포먼스트레이닝</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>lhj0709_@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1436-2922</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로15길 11 지층</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dyb_performance</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>59</v>
+      </c>
+      <c r="R65" t="n">
+        <v>116</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1667051610</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1667051610</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>070-8024-0922</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 미아동</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1356268668</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1356268668</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>근육케어 EMS 클럽</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>juh1357@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔매로45길 30 1층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>17</v>
+      </c>
+      <c r="R67" t="n">
+        <v>22</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1284736783</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1284736783</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>필라테스 케밍 수유점</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>keming_@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>kemingcompany@gmail.com</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1329-9609</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 322 3층</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://pilateskeming.com/</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>310</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>189</v>
+      </c>
+      <c r="R68" t="n">
+        <v>499</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1901646336</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1901646336</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>드로우짐 헬스&amp;PT 미아점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>drawgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1304-4992</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/drawgym</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>1289</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1949</v>
+      </c>
+      <c r="R69" t="n">
+        <v>3238</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1268963442</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1268963442</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>아이르 필라테스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>center_bb@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1341-7772</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 365 4층</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/iir.wellness</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>308</v>
+      </c>
+      <c r="R70" t="n">
+        <v>529</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1625791564</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1625791564</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>하이프핏, 수유PT샵</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>her__zz@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1301-9491</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hypedobby</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>40</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>2099905937</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2099905937</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>올바른PT 삼양사거리점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>olbareunpt4_@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1366-4502</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 166 2층</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/olbareunpt4_</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>180</v>
+      </c>
+      <c r="R72" t="n">
+        <v>269</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1034422634</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1034422634</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>다이어트모드 휘트니스 수유점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>dietmode-@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1301-8244</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 350 5층</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dietmode-</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>211</v>
+      </c>
+      <c r="R73" t="n">
+        <v>310</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>37637672</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37637672</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>아크로짐 24시 휘트니스 미아점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>acrogym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1489-9049</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/acrogym1</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>1936</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>828</v>
+      </c>
+      <c r="R74" t="n">
+        <v>2764</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1492139790</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1492139790</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>휘트니스피플 우먼 수유역점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>02-990-3912</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@fitnesspeople_woman?si=B4vpeivvu5fbYHvk</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>1717</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>389</v>
+      </c>
+      <c r="R75" t="n">
+        <v>2106</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1985390755</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1985390755</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>머슬엑스짐</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ask4554@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1370-4554</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ask4554</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>202</v>
+      </c>
+      <c r="R76" t="n">
+        <v>212</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1735126857</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1735126857</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>굿바디필라테스 EMS트레이닝PT</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>goodbodypila-emspt@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1402-2233</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 293 2층</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goodbodypila-emspt</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>17</v>
+      </c>
+      <c r="R77" t="n">
+        <v>81</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1408311287</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1408311287</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>바디코드 필라테스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>bodycode_suyu@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1491-5667</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 351 3층</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bodycode_suyu</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>397</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>242</v>
+      </c>
+      <c r="R78" t="n">
+        <v>639</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>1888853511</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1888853511</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>큐에이치필라테스&amp;PT더프리미엄 수유점</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>qh-03@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 358 2층 202호 큐에이치 필라테스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/qh-03</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>6</v>
+      </c>
+      <c r="R79" t="n">
+        <v>18</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>1397546953</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1397546953</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>모티오나 재활운동 센터</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>motiona_js8875@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1328-8875</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 노해로 113 지하1층</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/motiona_js8875</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>12</v>
+      </c>
+      <c r="R80" t="n">
+        <v>24</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>2050145894</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2050145894</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>범휘트니스  수유점</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>bum903@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0507-1409-0851</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 293</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bum903</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>20</v>
+      </c>
+      <c r="R81" t="n">
+        <v>57</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>13162791</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13162791</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>가설자재,비티아시바피티아시바,난간대파이프판매,임대설치</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>rodtmdu12@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>070-8174-8741</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 수유동</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>1338034788</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1338034788</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>F45 수유</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>f45_suyu@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 323 7층</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/f45suyu/</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>161</v>
+      </c>
+      <c r="R83" t="n">
+        <v>252</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>1853806359</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1853806359</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>97_cosat@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1467-8213</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 118 3층</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/97_cosat</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>547</v>
+      </c>
+      <c r="R84" t="n">
+        <v>709</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>1431265273</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1431265273</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>gorillagym5@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1420-9036</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 352 지하1층</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gorillagym5</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>689</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>728</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1417</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>38411705</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38411705</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>라이프플러스휘트니스 번동점</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>lifeplus1209@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1362-4534</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 오현로 194 지하1층</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lifeplus_bd/</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>694</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>144</v>
+      </c>
+      <c r="R86" t="n">
+        <v>838</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1877606346</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1877606346</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>피티아시바</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>unixgaseol7@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>070-5255-1081</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 우이동</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>1782336039</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1782336039</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>라이프빌딩PT</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>life_building_@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1404-1363</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lifebuildingpt/</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>532</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>2236</v>
+      </c>
+      <c r="R88" t="n">
+        <v>2768</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>1906517072</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1906517072</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>honeymusclegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1331-4021</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 130 2층</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@명희달려</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>91</v>
+      </c>
+      <c r="R89" t="n">
+        <v>177</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>1057899676</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1057899676</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>the GoodFit</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>goodfit9008@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goodfit9008</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>19</v>
+      </c>
+      <c r="R90" t="n">
+        <v>21</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>1222324632</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1222324632</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>스타필라테스</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>3007761@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1347-9979</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로13길 13 3층 스타필라테스</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/3007761</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>475</v>
+      </c>
+      <c r="R91" t="n">
+        <v>559</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>1573837078</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1573837078</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/강북_PT.xlsx
+++ b/naver-place-crawler/results_health/강북_PT.xlsx
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,20 +690,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wa2rxwt</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -774,7 +778,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dwgym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,20 +788,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4e814</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -868,7 +876,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifebuildingpt/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,7 +886,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -962,7 +970,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ready4gymsuyu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,20 +980,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcs9wn</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1000,10 +1012,10 @@
         <v>1086</v>
       </c>
       <c r="Q6" t="n">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="R6" t="n">
-        <v>1953</v>
+        <v>1956</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1094,10 +1106,10 @@
         <v>4548</v>
       </c>
       <c r="Q7" t="n">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="R7" t="n">
-        <v>5752</v>
+        <v>5753</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/강북_PT.xlsx
+++ b/naver-place-crawler/results_health/강북_PT.xlsx
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/97_cosat</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,24 +690,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wa2rxwt</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -744,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -778,7 +774,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dwgym1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,24 +784,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4e814</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -842,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -876,7 +868,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lifebuildingpt/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,7 +878,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -936,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -970,7 +962,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ready4gymsuyu</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -980,24 +972,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcs9wn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1009,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="Q6" t="n">
         <v>870</v>
       </c>
       <c r="R6" t="n">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1034,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1116,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/강북_PT.xlsx
+++ b/naver-place-crawler/results_health/강북_PT.xlsx
@@ -1000,10 +1000,10 @@
         <v>1085</v>
       </c>
       <c r="Q6" t="n">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="R6" t="n">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/강북_PT.xlsx
+++ b/naver-place-crawler/results_health/강북_PT.xlsx
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="39" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -718,10 +718,10 @@
         <v>24</v>
       </c>
       <c r="Q3" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R3" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dwgym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,20 +784,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4e814</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2659</v>
+        <v>2660</v>
       </c>
       <c r="Q4" t="n">
         <v>4787</v>
       </c>
       <c r="R4" t="n">
-        <v>7446</v>
+        <v>7447</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -868,7 +872,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifebuildingpt/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,7 +882,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -962,7 +966,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ready4gymsuyu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,20 +976,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcs9wn</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1000,10 +1008,10 @@
         <v>1085</v>
       </c>
       <c r="Q6" t="n">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="R6" t="n">
-        <v>1956</v>
+        <v>1959</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1056,7 +1064,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym33/223928936059</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,20 +1074,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43knh</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4548</v>
+        <v>4549</v>
       </c>
       <c r="Q7" t="n">
         <v>1205</v>
       </c>
       <c r="R7" t="n">
-        <v>5753</v>
+        <v>5754</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/강북_PT.xlsx
+++ b/naver-place-crawler/results_health/강북_PT.xlsx
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="39" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="47" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -718,10 +718,10 @@
         <v>24</v>
       </c>
       <c r="Q3" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="R3" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dwgym1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,24 +784,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4e814</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2660</v>
+        <v>2661</v>
       </c>
       <c r="Q4" t="n">
-        <v>4787</v>
+        <v>4794</v>
       </c>
       <c r="R4" t="n">
-        <v>7447</v>
+        <v>7455</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -838,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -872,7 +868,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lifebuildingpt/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -882,7 +878,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -932,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -966,7 +962,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ready4gymsuyu</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,24 +972,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcs9wn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1030,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1056,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ablegym33/223928936059</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1074,24 +1066,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43knh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1128,7 +1116,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/강북_PT.xlsx
+++ b/naver-place-crawler/results_health/강북_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
+          <t>핏의공식</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>uphoria6825@naver.com</t>
+          <t>gymseungeun@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1334-6825</t>
+          <t>0507-1458-1884</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
+          <t>서울특별시 강북구 한천로131길 17 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uphoria_mia_1/</t>
+          <t>https://www.instagram.com/gymseungeun/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>230</v>
+        <v>29</v>
       </c>
       <c r="Q2" t="n">
-        <v>584</v>
+        <v>47</v>
       </c>
       <c r="R2" t="n">
-        <v>814</v>
+        <v>76</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1037773645</t>
+          <t>2024627135</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037773645</t>
+          <t>https://m.place.naver.com/place/2024627135</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>짐코사트 헬스&amp;PT 수유점</t>
+          <t>데일리프리미엄 그룹PT샵 미아점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>dailygrouppt@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1308-4535</t>
+          <t>0507-1385-0454</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유로 81 3층</t>
+          <t>서울특별시 강북구 도봉로 98 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>https://www.instagram.com/luv.dailypt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="Q3" t="n">
-        <v>159</v>
+        <v>66</v>
       </c>
       <c r="R3" t="n">
-        <v>183</v>
+        <v>109</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1604797933</t>
+          <t>2069382925</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604797933</t>
+          <t>https://m.place.naver.com/place/2069382925</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+          <t>라이프플러스휘트니스 번동점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dwgym1@naver.com</t>
+          <t>lifeplus1209@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1370-7849</t>
+          <t>0507-1362-4534</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
+          <t>서울특별시 강북구 오현로 194 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dwgym1</t>
+          <t>https://www.instagram.com/lifeplus_bd/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2661</v>
+        <v>697</v>
       </c>
       <c r="Q4" t="n">
-        <v>4794</v>
+        <v>145</v>
       </c>
       <c r="R4" t="n">
-        <v>7455</v>
+        <v>842</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1284235115</t>
+          <t>1877606346</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284235115</t>
+          <t>https://m.place.naver.com/place/1877606346</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>라이프빌딩PT</t>
+          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>life_building_@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1404-1363</t>
+          <t>0507-1467-8213</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
+          <t>서울특별시 강북구 삼양로 118 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifebuildingpt/</t>
+          <t>https://blog.naver.com/97_cosat</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>532</v>
+        <v>162</v>
       </c>
       <c r="Q5" t="n">
-        <v>2236</v>
+        <v>554</v>
       </c>
       <c r="R5" t="n">
-        <v>2768</v>
+        <v>716</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1906517072</t>
+          <t>1431265273</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1906517072</t>
+          <t>https://m.place.naver.com/place/1431265273</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>레디포짐 헬스&amp;PT 수유점</t>
+          <t>아크로짐 24시 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ready4gymsuyu@naver.com</t>
+          <t>acrogym1@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1430-3344</t>
+          <t>0507-1489-9049</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
+          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ready4gymsuyu</t>
+          <t>https://blog.naver.com/acrogym1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1085</v>
+        <v>1939</v>
       </c>
       <c r="Q6" t="n">
-        <v>874</v>
+        <v>828</v>
       </c>
       <c r="R6" t="n">
-        <v>1959</v>
+        <v>2767</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>38648497</t>
+          <t>1492139790</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38648497</t>
+          <t>https://m.place.naver.com/place/1492139790</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>에이블짐 수유점</t>
+          <t>플로리다휘트니스 삼양동점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ablegym33@naver.com</t>
+          <t>sd670@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1340-7281</t>
+          <t>0507-1417-9917</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
+          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym33/223928936059</t>
+          <t>https://blog.naver.com/sd670</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4549</v>
+        <v>87</v>
       </c>
       <c r="Q7" t="n">
-        <v>1205</v>
+        <v>236</v>
       </c>
       <c r="R7" t="n">
-        <v>5754</v>
+        <v>323</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,15 +1106,7911 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
+          <t>33937785</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33937785</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>dwgym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1370-7849</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dwgym1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>2661</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4804</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7465</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1284235115</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1284235115</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>우주짐 미아점 PT &amp; 헬스</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>woojoogym@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1354-5063</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 173 지층</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://litt.ly/woojoogym</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>352</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>620</v>
+      </c>
+      <c r="R9" t="n">
+        <v>972</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1022408622</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1022408622</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>070-8024-0813</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 수유동</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1662868565</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1662868565</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>위핏헬스&amp;PT 수유역점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>wefit100@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1490-2127</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로139길 42 4층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_ZWKxjn</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>827</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>559</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1386</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1661637243</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1661637243</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>더블플러스휘트니스클럽</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>osbum0224@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1306-3451</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 인수봉로 293 2층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>13</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1035955167</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1035955167</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>가설자재,비티아시바피티아시바,난간대파이프판매,임대설치</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>rodtmdu12@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>070-8174-8741</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 수유동</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1338034788</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1338034788</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>노블휘트니스</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>noble_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1421-2221</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/noble_fitness</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>130</v>
+      </c>
+      <c r="R14" t="n">
+        <v>305</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>36246823</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36246823</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>프레스짐 헬스 &amp; PT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>codelegend@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1344-9688</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pressgym___</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>45</v>
+      </c>
+      <c r="R15" t="n">
+        <v>281</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1695685266</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1695685266</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>rkdqnr7184@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1336-7184</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_QERxeG</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>462</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>795</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1257</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1172555749</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1172555749</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>큐에이치필라테스&amp;PT더프리미엄 수유점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>qh-03@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 358 2층 202호 큐에이치 필라테스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/qh-03</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>18</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1397546953</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1397546953</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>서울가설재BT비티아시바PT피티아시바파이프비계임대시공판매</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>070-8075-1072</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 번동</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1764669223</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1764669223</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>장소대여</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>메노모쏘</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>nana_1982@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1375-4415</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로173길 21-6 1층</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1344980412</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1344980412</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>라이프빌딩PT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>life_building_@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1404-1363</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lifebuildingpt/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>532</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2236</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2768</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1906517072</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1906517072</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>체력단련,운동</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DL 운동센터</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gunwigun_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔매로22가길 11 2층 201호</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://litt.ly/d.l.trainer</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1479834103</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1479834103</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>하이엔드짐 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>highend_fit@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1417-2362</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로 1035 지하1층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://highendgymsuyu-landing.vercel.app</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>1816</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1185</v>
+      </c>
+      <c r="R22" t="n">
+        <v>3001</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1953510990</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1953510990</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>wellcare093@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1404-1390</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wellcare093</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>54</v>
+      </c>
+      <c r="R23" t="n">
+        <v>63</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2039688284</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2039688284</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>드로우짐 헬스&amp;PT 미아점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>drawgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1304-4992</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/drawgym</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>1291</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1958</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3249</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1268963442</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1268963442</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>짐박스피트니스 미아사거리역점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1391-2161</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://gymboxx.com/onceinayear?gym=79</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>1150</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>41</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1191</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2099546838</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2099546838</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>서울가설재BT비티아시바PT피티아시바파이프비계임대시공판매</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>070-8075-1025</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 미아동</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1003986024</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1003986024</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>피티아시바</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>unixgaseol7@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>070-5255-1081</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 우이동</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1782336039</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1782336039</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>제이핏 여성전용피티샵</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>lhj0709_@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>02-982-7707</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 188 5층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jjfit_7707</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>10</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>804545907</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/804545907</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>woojoogym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1362-5063</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/woojoo_gym2/</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>221</v>
+      </c>
+      <c r="R29" t="n">
+        <v>349</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2089127568</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2089127568</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>통증&amp;교정연구소</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>xtmxjax@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1318-2087</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로77길 6 910호</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/xtmxjax</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>10</v>
+      </c>
+      <c r="R30" t="n">
+        <v>43</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1975301409</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1975301409</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>버클필라테스&amp;PT 미아점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>buckle1234@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1485-1323</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_YLwxfn/chat</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>637</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>700</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1337</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1358291633</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1358291633</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>gorillagym5@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1420-9036</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 352 지하1층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gorillagym5</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>689</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>728</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1417</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>38411705</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38411705</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>헬스&amp;PT 건짐 수유역점</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>gungympt@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1459-7599</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 노해로 1 지하1층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gungympt</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>426</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>223</v>
+      </c>
+      <c r="R33" t="n">
+        <v>649</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1381178715</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1381178715</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>더 퍼스트짐</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ssdaw1234@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1353-7541</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로131길 29 3층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ssdaw1234</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>93</v>
+      </c>
+      <c r="R34" t="n">
+        <v>117</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1176777711</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1176777711</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>아이르 필라테스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>center_bb@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1341-7772</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 365 4층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/iir.wellness</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>308</v>
+      </c>
+      <c r="R35" t="n">
+        <v>529</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1625791564</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1625791564</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>휘트니스피플 우먼 수유역점</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>02-990-3912</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@fitnesspeople_woman?si=B4vpeivvu5fbYHvk</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>1720</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>404</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2124</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1985390755</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1985390755</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>레디포짐 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ready4gymsuyu@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1430-3344</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ready4gymsuyu</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>1086</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>878</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1964</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>38648497</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38648497</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>엘투휘트니스 수유번동점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>lhj0709_@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1369-2202</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>11</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2045876824</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2045876824</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>올레이디짐 가오리점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>hyomin_nase@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1369-0010</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 416 2층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://allladygym.imweb.me/</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>165</v>
+      </c>
+      <c r="R39" t="n">
+        <v>244</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1633562526</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1633562526</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>디와이비퍼포먼스트레이닝</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>lhj0709_@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1436-2922</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로15길 11 지층</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dyb_performance</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>58</v>
+      </c>
+      <c r="R40" t="n">
+        <v>115</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1667051610</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1667051610</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>라인짐휘트니스</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>linegym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1418-7007</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/linegym_</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>297</v>
+      </c>
+      <c r="R41" t="n">
+        <v>392</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>17944349</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/17944349</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>범휘트니스  수유점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>bum903@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1409-0851</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 293</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bum903</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>20</v>
+      </c>
+      <c r="R42" t="n">
+        <v>57</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>13162791</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13162791</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>빌리프짐 수유점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>beliefgym4@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1343-9679</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beliefgym_suyu/</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1621</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1197</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2818</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1058492468</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1058492468</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>모티오나 재활운동 센터</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>motiona_js8875@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1328-8875</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 노해로 113 지하1층</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/motiona_js8875</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>13</v>
+      </c>
+      <c r="R44" t="n">
+        <v>30</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2050145894</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2050145894</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>머슬엑스짐</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ask4554@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1370-4554</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ask4554</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>202</v>
+      </c>
+      <c r="R45" t="n">
+        <v>212</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1735126857</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1735126857</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>070-8024-0922</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 미아동</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1356268668</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1356268668</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>스포애니 수유역점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>spoany52@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1310-9628</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spoany52</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>2755</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2356</v>
+      </c>
+      <c r="R47" t="n">
+        <v>5111</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1440007035</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1440007035</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>프리원핏 미아점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>lhj0709_@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1380-1962</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/freewantfit__mia/</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>94</v>
+      </c>
+      <c r="R48" t="n">
+        <v>169</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2037364243</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2037364243</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>포레스트PT짐</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>forestgym24@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/forestgym24/223778254580</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>7</v>
+      </c>
+      <c r="R49" t="n">
+        <v>28</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1008319723</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1008319723</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>근육케어 EMS 클럽</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>juh1357@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔매로45길 30 1층</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>17</v>
+      </c>
+      <c r="R50" t="n">
+        <v>22</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1284736783</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1284736783</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>에이블짐 수유점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ablegym33@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1340-7281</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ablegym33/223928936059</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>4553</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1195</v>
+      </c>
+      <c r="R51" t="n">
+        <v>5748</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
           <t>1745960523</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1745960523</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>피티아시바</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>unixgaseol7@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>070-5255-1240</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 미아동</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1012926496</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1012926496</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>애드TOP</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>deoj4628@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>070-8227-7372</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 166</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>30824060</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/30824060</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>바디코드 필라테스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>bodycode_suyu@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1491-5667</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 351 3층</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bodycode_suyu</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>397</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>242</v>
+      </c>
+      <c r="R54" t="n">
+        <v>639</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1888853511</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1888853511</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>바디채널 광산사거리점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>bodyfit_@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1359-6850</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bodychannel_kwangsan/?hl=ko</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>320</v>
+      </c>
+      <c r="R55" t="n">
+        <v>421</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1089484623</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1089484623</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>파인드미짐 헬스&amp;PT 수유역점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>find_me_pt_studio@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1478-5103</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로144길 11 2층</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/find_me_pt_studio</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>226</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>421</v>
+      </c>
+      <c r="R56" t="n">
+        <v>647</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1116831923</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1116831923</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>honeymusclegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>myeonghui5402@gmail.com</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1331-4021</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 130 2층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@명희달려</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>91</v>
+      </c>
+      <c r="R57" t="n">
+        <v>177</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1057899676</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1057899676</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>존버짐 미아뉴타운점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>jonbergym3@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1368-4511</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jonbergym3</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>220</v>
+      </c>
+      <c r="R58" t="n">
+        <v>298</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1293414126</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1293414126</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>goodfit9008@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goodfit9008</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>248</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1343</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1591</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1850055844</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1850055844</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>굿바디필라테스 EMS트레이닝PT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>goodbodypila-emspt@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1402-2233</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 293 2층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goodbodypila-emspt</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>17</v>
+      </c>
+      <c r="R60" t="n">
+        <v>81</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1408311287</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1408311287</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>데일리PT샵 미아본점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>dailypt0926@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1362-0934</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 98</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dailypt0926</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1304</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1382</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1069239956</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1069239956</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>하이프핏, 수유PT샵</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>her__zz@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1301-9491</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hypedobby</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>43</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>2099905937</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2099905937</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>밀리언짐 수유점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>milliongym-suyu@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1357-9092</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/milliongym-suyu</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>61</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>2061019894</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2061019894</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>가설재비티아시바피티아시바파이프유로폼임대대여설치</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>rodtmdu12@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>070-8069-0779</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 번동</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1752172206</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1752172206</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>스타필라테스</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>3007761@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1347-9979</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로13길 13 3층 스타필라테스</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/3007761</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>490</v>
+      </c>
+      <c r="R65" t="n">
+        <v>574</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1573837078</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1573837078</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>수유 재활운동센터 라이프리턴</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>lifereturn_suyu@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1377-5126</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_ExmdAX</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>56</v>
+      </c>
+      <c r="R66" t="n">
+        <v>78</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>2013060255</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2013060255</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>피트니스 베네핏 수유역점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>baekyuri802@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1351-2438</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/baekyuri802</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>623</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>339</v>
+      </c>
+      <c r="R67" t="n">
+        <v>962</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1550724103</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1550724103</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>올바른PT 삼양사거리점</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>olbareunpt4_@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1366-4502</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 삼양로 166 2층</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/olbareunpt4_</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>180</v>
+      </c>
+      <c r="R68" t="n">
+        <v>269</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1034422634</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1034422634</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>lifebuildingmia@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1332-1672</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 136 9층</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://landing-mia-ebon.vercel.app/</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>582</v>
+      </c>
+      <c r="R69" t="n">
+        <v>903</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>36362933</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36362933</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>소울휘트니스</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>h9a1n94@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>02-985-5553</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/h9a1n94</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>335</v>
+      </c>
+      <c r="R70" t="n">
+        <v>450</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>37240884</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37240884</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>에너메카 휘트니스 미아점</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>nyh314@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1344-1650</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nyh314</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>334</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>365</v>
+      </c>
+      <c r="R71" t="n">
+        <v>699</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>37615690</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37615690</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>에스핏 휘트니스 수유점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>kdhonepick@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1393-8101</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로67길 18 3층</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kdhonepick</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>243</v>
+      </c>
+      <c r="R72" t="n">
+        <v>359</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1185739926</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1185739926</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>블랙핏pt샵 미아사거리점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>blackfit123@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1309-1030</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/blackfit123</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>375</v>
+      </c>
+      <c r="R73" t="n">
+        <v>521</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1105932712</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1105932712</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>가설자재비티아시바피티아시바발안전난간대판매임대설치</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>rodtmdu12@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>070-8083-6616</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 수유동</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1740427970</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1740427970</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>짐초이 헬스&amp;PT 수유역점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>gymchoi@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1321-8296</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 덕릉로 99 제지하1층 101호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gymchoi</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>348</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>345</v>
+      </c>
+      <c r="R75" t="n">
+        <v>693</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1548872331</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1548872331</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>드림유어바디 필라테스 미아점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>popleedon@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로15길 11 3,4층 (드림유어바디)</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dyb_pilates/</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>1264</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>239</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1503</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>11630404</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11630404</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>osbum0224@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>02-986-2534</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>http://www.thebarunfitness.com</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>104</v>
+      </c>
+      <c r="R77" t="n">
+        <v>184</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>38636716</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38636716</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>가설재비티아시바피티아시바파이프유로폼임대대여설치</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>rodtmdu12@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>070-8069-0778</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 미아동</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>1022266242</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1022266242</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>필라테스 케밍 수유점</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>keming_@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>kemingcompany@gmail.com</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1329-9609</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 322 3층</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://pilateskeming.com/</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>312</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>189</v>
+      </c>
+      <c r="R79" t="n">
+        <v>501</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>1901646336</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1901646336</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>다이어트모드 휘트니스 수유점</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>dietmode-@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1301-8244</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 350 5층</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dietmode-</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>211</v>
+      </c>
+      <c r="R80" t="n">
+        <v>310</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>37637672</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37637672</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>트렌디우먼휘트니스 미아사거리역점</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>trend_hd4@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>02-988-3124</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/trend_hd4</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>2270</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1440</v>
+      </c>
+      <c r="R81" t="n">
+        <v>3710</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1885902314</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1885902314</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>uphoria6825@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1334-6825</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/uphoria_mia_1/</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>584</v>
+      </c>
+      <c r="R82" t="n">
+        <v>814</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>1037773645</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1037773645</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>판타스틱짐 수유점 여성전용피트니스</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>blueskirt0704@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1338-1501</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/blueskirt0704</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>523</v>
+      </c>
+      <c r="R83" t="n">
+        <v>665</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>1914282686</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1914282686</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>짐코사트 헬스&amp;PT 수유점</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>97_cosat@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1308-4535</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 수유로 81 3층</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/97_cosat</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>162</v>
+      </c>
+      <c r="R84" t="n">
+        <v>186</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>1604797933</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1604797933</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>the GoodFit</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>goodfit9008@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goodfit9008</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>19</v>
+      </c>
+      <c r="R85" t="n">
+        <v>21</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1222324632</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1222324632</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>F45 수유</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>f45_suyu@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 323 7층</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wy43x6v</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>162</v>
+      </c>
+      <c r="R86" t="n">
+        <v>253</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1853806359</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1853806359</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>크로스핏 알앤엘 수유</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>crossfitrnl_su@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1382-4849</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 덕릉로 76 B1</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4zmep</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>194</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>501</v>
+      </c>
+      <c r="R87" t="n">
+        <v>695</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>31777480</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31777480</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>스포애니 삼양사거리점</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>spoany87@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1338-9618</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sak0</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>1465</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1729</v>
+      </c>
+      <c r="R88" t="n">
+        <v>3194</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>1790576623</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1790576623</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>엑시스피티</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>axis_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1339-8603</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로8길 33 2층</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wwrhsu4</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>46</v>
+      </c>
+      <c r="R89" t="n">
+        <v>71</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>2055534881</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2055534881</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>이성현퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>sunghyunle2@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1437-5900</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sunghyunle2</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>29</v>
+      </c>
+      <c r="R90" t="n">
+        <v>61</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>35384521</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35384521</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>에너메카휘트니스 미아사거리점</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>nyh314@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1320-7744</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcha8q</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>1339</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>885</v>
+      </c>
+      <c r="R91" t="n">
+        <v>2224</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>1756863852</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1756863852</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/강북_PT.xlsx
+++ b/naver-place-crawler/results_health/강북_PT.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>핏의공식</t>
+          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>gymseungeun@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1458-1884</t>
+          <t>0507-1467-8213</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 17 4층</t>
+          <t>서울특별시 강북구 삼양로 118 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gymseungeun/</t>
+          <t>https://blog.naver.com/97_cosat</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>29</v>
+        <v>162</v>
       </c>
       <c r="Q2" t="n">
-        <v>47</v>
+        <v>554</v>
       </c>
       <c r="R2" t="n">
-        <v>76</v>
+        <v>716</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2024627135</t>
+          <t>1431265273</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024627135</t>
+          <t>https://m.place.naver.com/place/1431265273</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>데일리프리미엄 그룹PT샵 미아점</t>
+          <t>아크로짐 24시 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dailygrouppt@naver.com</t>
+          <t>acrogym1@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1385-0454</t>
+          <t>0507-1489-9049</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98 3층</t>
+          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luv.dailypt</t>
+          <t>https://blog.naver.com/acrogym1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>43</v>
+        <v>1940</v>
       </c>
       <c r="Q3" t="n">
-        <v>66</v>
+        <v>828</v>
       </c>
       <c r="R3" t="n">
-        <v>109</v>
+        <v>2768</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +730,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2069382925</t>
+          <t>1492139790</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2069382925</t>
+          <t>https://m.place.naver.com/place/1492139790</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>라이프플러스휘트니스 번동점</t>
+          <t>이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lifeplus1209@naver.com</t>
+          <t>sunghyunle2@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1362-4534</t>
+          <t>0507-1437-5900</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오현로 194 지하1층</t>
+          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifeplus_bd/</t>
+          <t>https://www.instagram.com/sunghyunle2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>697</v>
+        <v>32</v>
       </c>
       <c r="Q4" t="n">
-        <v>145</v>
+        <v>29</v>
       </c>
       <c r="R4" t="n">
-        <v>842</v>
+        <v>61</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1877606346</t>
+          <t>35384521</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1877606346</t>
+          <t>https://m.place.naver.com/place/35384521</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -846,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>짐코사트 필라테스&amp;PT 삼양사거리점</t>
+          <t>수유 재활운동센터 라이프리턴</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>lifereturn_suyu@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1467-8213</t>
+          <t>0507-1377-5126</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 118 3층</t>
+          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>https://pf.kakao.com/_ExmdAX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -894,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>162</v>
+        <v>22</v>
       </c>
       <c r="Q5" t="n">
-        <v>554</v>
+        <v>57</v>
       </c>
       <c r="R5" t="n">
-        <v>716</v>
+        <v>79</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +918,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1431265273</t>
+          <t>2013060255</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1431265273</t>
+          <t>https://m.place.naver.com/place/2013060255</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>아크로짐 24시 휘트니스 미아점</t>
+          <t>하이프핏, 수유PT샵</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>acrogym1@naver.com</t>
+          <t>her__zz@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1489-9049</t>
+          <t>0507-1301-9491</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 223 4층 아크로짐 미아점</t>
+          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acrogym1</t>
+          <t>https://www.instagram.com/hypedobby</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1939</v>
+        <v>43</v>
       </c>
       <c r="Q6" t="n">
-        <v>828</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2767</v>
+        <v>43</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1492139790</t>
+          <t>2099905937</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1492139790</t>
+          <t>https://m.place.naver.com/place/2099905937</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>플로리다휘트니스 삼양동점</t>
+          <t>드로우짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sd670@naver.com</t>
+          <t>drawgym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1417-9917</t>
+          <t>0507-1304-4992</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
+          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sd670</t>
+          <t>https://blog.naver.com/drawgym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>87</v>
+        <v>1291</v>
       </c>
       <c r="Q7" t="n">
-        <v>236</v>
+        <v>1958</v>
       </c>
       <c r="R7" t="n">
-        <v>323</v>
+        <v>3249</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1106,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>33937785</t>
+          <t>1268963442</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33937785</t>
+          <t>https://m.place.naver.com/place/1268963442</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
+          <t>가설재비티아시바피티아시바파이프유로폼임대대여설치</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dwgym1@naver.com</t>
+          <t>rodtmdu12@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1370-7849</t>
+          <t>070-8069-0778</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dwgym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2661</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4804</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>7465</v>
+        <v>0</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1284235115</t>
+          <t>1022266242</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284235115</t>
+          <t>https://m.place.naver.com/place/1022266242</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1222,34 +1222,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>우주짐 미아점 PT &amp; 헬스</t>
+          <t>라인짐휘트니스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>woojoogym@naver.com</t>
+          <t>linegym_@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1354-5063</t>
+          <t>0507-1418-7007</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 173 지층</t>
+          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://litt.ly/woojoogym</t>
+          <t>https://blog.naver.com/linegym_</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>352</v>
+        <v>95</v>
       </c>
       <c r="Q9" t="n">
-        <v>620</v>
+        <v>297</v>
       </c>
       <c r="R9" t="n">
-        <v>972</v>
+        <v>392</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1294,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1022408622</t>
+          <t>17944349</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1022408622</t>
+          <t>https://m.place.naver.com/place/17944349</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>건축,토목</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+          <t>판타스틱짐 수유점 여성전용피트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>blueskirt0704@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>070-8024-0813</t>
+          <t>0507-1338-1501</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유동</t>
+          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/blueskirt0704</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>666</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,61 +1388,61 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1662868565</t>
+          <t>1914282686</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1662868565</t>
+          <t>https://m.place.naver.com/place/1914282686</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장소대여</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>위핏헬스&amp;PT 수유역점</t>
+          <t>메노모쏘</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wefit100@naver.com</t>
+          <t>nana_1982@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1490-2127</t>
+          <t>0507-1375-4415</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로139길 42 4층</t>
+          <t>서울특별시 강북구 삼양로173길 21-6 1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ZWKxjn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1458,22 +1458,22 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>827</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1386</v>
+        <v>2</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1661637243</t>
+          <t>1344980412</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1661637243</t>
+          <t>https://m.place.naver.com/place/1344980412</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1504,29 +1504,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>더블플러스휘트니스클럽</t>
+          <t>파인드미짐 헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>osbum0224@naver.com</t>
+          <t>find_me_pt_studio@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1306-3451</t>
+          <t>0507-1478-5103</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 인수봉로 293 2층</t>
+          <t>서울특별시 강북구 한천로144길 11 2층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/find_me_pt_studio</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1552,22 +1552,22 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7</v>
+        <v>226</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>421</v>
       </c>
       <c r="R12" t="n">
-        <v>13</v>
+        <v>647</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,51 +1576,47 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1035955167</t>
+          <t>1116831923</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1035955167</t>
+          <t>https://m.place.naver.com/place/1116831923</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>가설자재,비티아시바피티아시바,난간대파이프판매,임대설치</t>
+          <t>드림유어바디 필라테스 미아점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>rodtmdu12@naver.com</t>
+          <t>popleedon@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>070-8174-8741</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유동</t>
+          <t>서울특별시 강북구 도봉로15길 11 3,4층 (드림유어바디)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/dyb_pilates/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1630,7 +1626,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1651,17 +1647,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1264</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1503</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,17 +1666,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1338034788</t>
+          <t>11630404</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338034788</t>
+          <t>https://m.place.naver.com/place/11630404</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1692,34 +1688,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>노블휘트니스</t>
+          <t>우주짐 미아점 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>noble_fitness@naver.com</t>
+          <t>woojoogym@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1421-2221</t>
+          <t>0507-1354-5063</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
+          <t>서울특별시 강북구 도봉로 173 지층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/noble_fitness</t>
+          <t>https://litt.ly/woojoogym</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1729,7 +1725,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1749,13 +1745,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>175</v>
+        <v>352</v>
       </c>
       <c r="Q14" t="n">
-        <v>130</v>
+        <v>620</v>
       </c>
       <c r="R14" t="n">
-        <v>305</v>
+        <v>972</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,56 +1760,56 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>36246823</t>
+          <t>1022408622</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36246823</t>
+          <t>https://m.place.naver.com/place/1022408622</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>프레스짐 헬스 &amp; PT</t>
+          <t>버클필라테스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>codelegend@naver.com</t>
+          <t>buckle1234@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1344-9688</t>
+          <t>0507-1485-1323</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
+          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pressgym___</t>
+          <t>http://pf.kakao.com/_YLwxfn/chat</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1834,7 +1830,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1843,13 +1839,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>236</v>
+        <v>636</v>
       </c>
       <c r="Q15" t="n">
-        <v>45</v>
+        <v>700</v>
       </c>
       <c r="R15" t="n">
-        <v>281</v>
+        <v>1336</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1858,61 +1854,61 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1695685266</t>
+          <t>1358291633</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695685266</t>
+          <t>https://m.place.naver.com/place/1358291633</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>건축,토목</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rkdqnr7184@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1336-7184</t>
+          <t>070-8024-0813</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
+          <t>서울특별시 강북구 수유동</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_QERxeG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1928,22 +1924,22 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>462</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>795</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1257</v>
+        <v>0</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1952,52 +1948,56 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1172555749</t>
+          <t>1662868565</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1172555749</t>
+          <t>https://m.place.naver.com/place/1662868565</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>큐에이치필라테스&amp;PT더프리미엄 수유점</t>
+          <t>헬스&amp;PT 건짐 수유역점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>qh-03@naver.com</t>
+          <t>gungympt@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1459-7599</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 358 2층 202호 큐에이치 필라테스&amp;PT 수유점</t>
+          <t>서울특별시 강북구 노해로 1 지하1층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/qh-03</t>
+          <t>https://www.instagram.com/gungympt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2018,7 +2018,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2027,13 +2027,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>426</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>223</v>
       </c>
       <c r="R17" t="n">
-        <v>18</v>
+        <v>649</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,51 +2042,51 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1397546953</t>
+          <t>1381178715</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1397546953</t>
+          <t>https://m.place.naver.com/place/1381178715</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>서울가설재BT비티아시바PT피티아시바파이프비계임대시공판매</t>
+          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>woojoogym2@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>070-8075-1072</t>
+          <t>0507-1362-5063</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 번동</t>
+          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/woojoo_gym2/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2117,17 +2117,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>222</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>351</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,51 +2136,51 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1764669223</t>
+          <t>2089127568</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1764669223</t>
+          <t>https://m.place.naver.com/place/2089127568</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>장소대여</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>메노모쏘</t>
+          <t>엑시스피티</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nana_1982@naver.com</t>
+          <t>axis_pt@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1375-4415</t>
+          <t>0507-1339-8603</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로173길 21-6 1층</t>
+          <t>서울특별시 강북구 도봉로8길 33 2층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/axis_pt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2206,22 +2206,22 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2230,17 +2230,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1344980412</t>
+          <t>2055534881</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1344980412</t>
+          <t>https://m.place.naver.com/place/2055534881</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2252,29 +2252,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>라이프빌딩PT</t>
+          <t>짐코사트 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>life_building_@naver.com</t>
+          <t>97_cosat@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1404-1363</t>
+          <t>0507-1308-4535</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
+          <t>서울특별시 강북구 수유로 81 3층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifebuildingpt/</t>
+          <t>https://blog.naver.com/97_cosat</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>532</v>
+        <v>24</v>
       </c>
       <c r="Q20" t="n">
-        <v>2236</v>
+        <v>159</v>
       </c>
       <c r="R20" t="n">
-        <v>2768</v>
+        <v>183</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,52 +2324,56 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1906517072</t>
+          <t>1604797933</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1906517072</t>
+          <t>https://m.place.naver.com/place/1604797933</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>체력단련,운동</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DL 운동센터</t>
+          <t>피트니스 베네핏 수유역점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>gunwigun_official@naver.com</t>
+          <t>baekyuri802@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1351-2438</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로22가길 11 2층 201호</t>
+          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://litt.ly/d.l.trainer</t>
+          <t>https://blog.naver.com/baekyuri802</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2379,7 +2383,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2390,7 +2394,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2399,13 +2403,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>623</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>339</v>
       </c>
       <c r="R21" t="n">
-        <v>6</v>
+        <v>962</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2414,17 +2418,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1479834103</t>
+          <t>1550724103</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1479834103</t>
+          <t>https://m.place.naver.com/place/1550724103</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2436,39 +2440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>하이엔드짐 헬스&amp;PT 수유점</t>
+          <t>스포애니 삼양사거리점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>highend_fit@naver.com</t>
+          <t>spoany87@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1417-2362</t>
+          <t>0507-1338-9618</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1035 지하1층</t>
+          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://highendgymsuyu-landing.vercel.app</t>
+          <t>https://blog.naver.com/spoany87</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2493,13 +2497,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1816</v>
+        <v>1465</v>
       </c>
       <c r="Q22" t="n">
-        <v>1185</v>
+        <v>1730</v>
       </c>
       <c r="R22" t="n">
-        <v>3001</v>
+        <v>3195</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2508,51 +2512,51 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1953510990</t>
+          <t>1790576623</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1953510990</t>
+          <t>https://m.place.naver.com/place/1790576623</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
+          <t>스포애니 수유역점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>wellcare093@naver.com</t>
+          <t>spoany52@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1404-1390</t>
+          <t>0507-1310-9628</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wellcare093</t>
+          <t>https://blog.naver.com/spoany52</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2583,17 +2587,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>9</v>
+        <v>2760</v>
       </c>
       <c r="Q23" t="n">
-        <v>54</v>
+        <v>2360</v>
       </c>
       <c r="R23" t="n">
-        <v>63</v>
+        <v>5120</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,51 +2606,51 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2039688284</t>
+          <t>1440007035</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039688284</t>
+          <t>https://m.place.naver.com/place/1440007035</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>건축,토목</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>드로우짐 헬스&amp;PT 미아점</t>
+          <t>피티아시바</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>drawgym@naver.com</t>
+          <t>unixgaseol7@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1304-4992</t>
+          <t>070-5255-1081</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 254 지하 1층</t>
+          <t>서울특별시 강북구 우이동</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/drawgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2656,12 +2660,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2677,17 +2681,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1291</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1958</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3249</v>
+        <v>0</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2696,60 +2700,56 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1268963442</t>
+          <t>1782336039</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1268963442</t>
+          <t>https://m.place.naver.com/place/1782336039</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>짐박스피트니스 미아사거리역점</t>
+          <t>데일리PT샵 미아본점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>dailypt0926@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1391-2161</t>
+          <t>0507-1362-0934</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 52</t>
+          <t>서울특별시 강북구 도봉로 98</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=79</t>
+          <t>https://blog.naver.com/dailypt0926</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2770,7 +2770,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2779,13 +2779,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1150</v>
+        <v>78</v>
       </c>
       <c r="Q25" t="n">
-        <v>41</v>
+        <v>1305</v>
       </c>
       <c r="R25" t="n">
-        <v>1191</v>
+        <v>1383</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2794,51 +2794,51 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2099546838</t>
+          <t>1069239956</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099546838</t>
+          <t>https://m.place.naver.com/place/1069239956</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>서울가설재BT비티아시바PT피티아시바파이프비계임대시공판매</t>
+          <t>데일리프리미엄 그룹PT샵 미아점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>dailygrouppt@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>070-8075-1025</t>
+          <t>0507-1385-0454</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 도봉로 98 3층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/luv.dailypt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2869,17 +2869,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1003986024</t>
+          <t>2069382925</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1003986024</t>
+          <t>https://m.place.naver.com/place/2069382925</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2910,24 +2910,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>피티아시바</t>
+          <t>가설자재비티아시바피티아시바발안전난간대판매임대설치</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>unixgaseol7@naver.com</t>
+          <t>rodtmdu12@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>070-5255-1081</t>
+          <t>070-8083-6616</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 우이동</t>
+          <t>서울특별시 강북구 수유동</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2982,17 +2982,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1782336039</t>
+          <t>1740427970</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1782336039</t>
+          <t>https://m.place.naver.com/place/1740427970</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3004,29 +3004,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>제이핏 여성전용피티샵</t>
+          <t>에너메카 휘트니스 미아점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>lhj0709_@naver.com</t>
+          <t>nyh314@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>02-982-7707</t>
+          <t>0507-1344-1650</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 188 5층</t>
+          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jjfit_7707</t>
+          <t>https://blog.naver.com/nyh314</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3057,17 +3057,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>10</v>
+        <v>334</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="R28" t="n">
-        <v>10</v>
+        <v>699</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3076,51 +3076,51 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>804545907</t>
+          <t>37615690</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/804545907</t>
+          <t>https://m.place.naver.com/place/37615690</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>우주짐 미아 2호점 PT &amp; 헬스</t>
+          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>woojoogym2@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1362-5063</t>
+          <t>02-986-2534</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 167 국민은행건물 4층</t>
+          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/woojoo_gym2/</t>
+          <t>http://www.thebarunfitness.com</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3155,13 +3155,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="Q29" t="n">
-        <v>221</v>
+        <v>104</v>
       </c>
       <c r="R29" t="n">
-        <v>349</v>
+        <v>184</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3170,17 +3170,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2089127568</t>
+          <t>38636716</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089127568</t>
+          <t>https://m.place.naver.com/place/38636716</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3192,29 +3192,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>통증&amp;교정연구소</t>
+          <t>블랙핏pt샵 미아사거리점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>xtmxjax@naver.com</t>
+          <t>blackfit123@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1318-2087</t>
+          <t>0507-1309-1030</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 910호</t>
+          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/xtmxjax</t>
+          <t>https://blog.naver.com/blackfit123</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3245,17 +3245,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>33</v>
+        <v>146</v>
       </c>
       <c r="Q30" t="n">
-        <v>10</v>
+        <v>375</v>
       </c>
       <c r="R30" t="n">
-        <v>43</v>
+        <v>521</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3264,61 +3264,61 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1975301409</t>
+          <t>1105932712</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1975301409</t>
+          <t>https://m.place.naver.com/place/1105932712</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>건축,토목</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>버클필라테스&amp;PT 미아점</t>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>buckle1234@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1485-1323</t>
+          <t>070-8024-0922</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 204 3층 버클필라테스</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_YLwxfn/chat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3334,22 +3334,22 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>637</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1337</v>
+        <v>0</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3358,51 +3358,51 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1358291633</t>
+          <t>1356268668</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358291633</t>
+          <t>https://m.place.naver.com/place/1356268668</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
+          <t>아이르 필라테스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>gorillagym5@naver.com</t>
+          <t>center_bb@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1420-9036</t>
+          <t>0507-1341-7772</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 지하1층</t>
+          <t>서울특별시 강북구 도봉로 365 4층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gorillagym5</t>
+          <t>https://www.instagram.com/iir.wellness</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3437,13 +3437,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>689</v>
+        <v>221</v>
       </c>
       <c r="Q32" t="n">
-        <v>728</v>
+        <v>308</v>
       </c>
       <c r="R32" t="n">
-        <v>1417</v>
+        <v>529</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3452,51 +3452,51 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>38411705</t>
+          <t>1625791564</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38411705</t>
+          <t>https://m.place.naver.com/place/1625791564</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>헬스&amp;PT 건짐 수유역점</t>
+          <t>통증&amp;교정연구소</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>gungympt@naver.com</t>
+          <t>xtmxjax@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1459-7599</t>
+          <t>0507-1318-2087</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 1 지하1층</t>
+          <t>서울특별시 강북구 도봉로77길 6 910호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gungympt</t>
+          <t>https://blog.naver.com/xtmxjax</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3527,17 +3527,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>426</v>
+        <v>33</v>
       </c>
       <c r="Q33" t="n">
-        <v>223</v>
+        <v>10</v>
       </c>
       <c r="R33" t="n">
-        <v>649</v>
+        <v>43</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3546,17 +3546,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1381178715</t>
+          <t>1975301409</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381178715</t>
+          <t>https://m.place.naver.com/place/1975301409</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3568,29 +3568,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>더 퍼스트짐</t>
+          <t>고릴라멀티짐 헬스 PT 골프 수유점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ssdaw1234@naver.com</t>
+          <t>gorillagym5@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1353-7541</t>
+          <t>0507-1420-9036</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 29 3층</t>
+          <t>서울특별시 강북구 도봉로 352 지하1층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ssdaw1234</t>
+          <t>https://blog.naver.com/gorillagym5</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3625,13 +3625,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>24</v>
+        <v>689</v>
       </c>
       <c r="Q34" t="n">
-        <v>93</v>
+        <v>728</v>
       </c>
       <c r="R34" t="n">
-        <v>117</v>
+        <v>1417</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3640,56 +3640,56 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1176777711</t>
+          <t>38411705</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1176777711</t>
+          <t>https://m.place.naver.com/place/38411705</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>아이르 필라테스&amp;PT 수유점</t>
+          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>center_bb@naver.com</t>
+          <t>lifebuildingmia@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1341-7772</t>
+          <t>0507-1332-1672</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 365 4층</t>
+          <t>서울특별시 강북구 도봉로 136 9층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/iir.wellness</t>
+          <t>https://landing-mia-ebon.vercel.app/</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3710,7 +3710,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3719,13 +3719,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>221</v>
+        <v>321</v>
       </c>
       <c r="Q35" t="n">
-        <v>308</v>
+        <v>583</v>
       </c>
       <c r="R35" t="n">
-        <v>529</v>
+        <v>904</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3734,17 +3734,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1625791564</t>
+          <t>36362933</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1625791564</t>
+          <t>https://m.place.naver.com/place/36362933</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3756,29 +3756,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 수유역점</t>
+          <t>밀리언짐 수유점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>milliongym-suyu@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>02-990-3912</t>
+          <t>0507-1357-9092</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
+          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://youtube.com/@fitnesspeople_woman?si=B4vpeivvu5fbYHvk</t>
+          <t>https://blog.naver.com/milliongym-suyu</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3813,13 +3813,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1720</v>
+        <v>61</v>
       </c>
       <c r="Q36" t="n">
-        <v>404</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>2124</v>
+        <v>62</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3828,17 +3828,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1985390755</t>
+          <t>2061019894</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985390755</t>
+          <t>https://m.place.naver.com/place/2061019894</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3850,29 +3850,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>레디포짐 헬스&amp;PT 수유점</t>
+          <t>머슬엑스짐</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ready4gymsuyu@naver.com</t>
+          <t>ask4554@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1430-3344</t>
+          <t>0507-1370-4554</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
+          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ready4gymsuyu</t>
+          <t>https://blog.naver.com/ask4554</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3903,17 +3903,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1086</v>
+        <v>10</v>
       </c>
       <c r="Q37" t="n">
-        <v>878</v>
+        <v>202</v>
       </c>
       <c r="R37" t="n">
-        <v>1964</v>
+        <v>212</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3922,51 +3922,51 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>38648497</t>
+          <t>1735126857</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38648497</t>
+          <t>https://m.place.naver.com/place/1735126857</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>엘투휘트니스 수유번동점</t>
+          <t>올바른PT 삼양사거리점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>lhj0709_@naver.com</t>
+          <t>olbareunpt4_@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1369-2202</t>
+          <t>0507-1366-4502</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
+          <t>서울특별시 강북구 삼양로 166 2층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/olbareunpt4_</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="R38" t="n">
-        <v>11</v>
+        <v>269</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4016,51 +4016,51 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2045876824</t>
+          <t>1034422634</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045876824</t>
+          <t>https://m.place.naver.com/place/1034422634</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>올레이디짐 가오리점</t>
+          <t>위핏헬스&amp;PT 수유역점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>hyomin_nase@naver.com</t>
+          <t>wefit100@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1369-0010</t>
+          <t>0507-1490-2127</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 416 2층</t>
+          <t>서울특별시 강북구 한천로139길 42 4층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://allladygym.imweb.me/</t>
+          <t>http://pf.kakao.com/_ZWKxjn</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4086,7 +4086,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4095,13 +4095,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>79</v>
+        <v>831</v>
       </c>
       <c r="Q39" t="n">
-        <v>165</v>
+        <v>560</v>
       </c>
       <c r="R39" t="n">
-        <v>244</v>
+        <v>1391</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4110,17 +4110,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1633562526</t>
+          <t>1661637243</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1633562526</t>
+          <t>https://m.place.naver.com/place/1661637243</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4132,29 +4132,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>디와이비퍼포먼스트레이닝</t>
+          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>lhj0709_@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0507-1436-2922</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로15길 11 지층</t>
+          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dyb_performance</t>
+          <t>https://blog.naver.com/goodfit9008</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4169,7 +4165,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4189,13 +4185,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>57</v>
+        <v>248</v>
       </c>
       <c r="Q40" t="n">
-        <v>58</v>
+        <v>1343</v>
       </c>
       <c r="R40" t="n">
-        <v>115</v>
+        <v>1591</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4204,51 +4200,51 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1667051610</t>
+          <t>1850055844</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1667051610</t>
+          <t>https://m.place.naver.com/place/1850055844</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>라인짐휘트니스</t>
+          <t>스타필라테스</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>linegym_@naver.com</t>
+          <t>3007761@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1418-7007</t>
+          <t>0507-1347-9979</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로109길 53 5층 라인짐휘트니스</t>
+          <t>서울특별시 강북구 도봉로13길 13 3층 스타필라테스</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/linegym_</t>
+          <t>https://blog.naver.com/3007761</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4283,13 +4279,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="Q41" t="n">
-        <v>297</v>
+        <v>491</v>
       </c>
       <c r="R41" t="n">
-        <v>392</v>
+        <v>575</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4298,17 +4294,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>17944349</t>
+          <t>1573837078</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17944349</t>
+          <t>https://m.place.naver.com/place/1573837078</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4320,29 +4316,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>범휘트니스  수유점</t>
+          <t>제이핏 여성전용피티샵</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>bum903@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1409-0851</t>
+          <t>02-982-7707</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 293</t>
+          <t>서울특별시 강북구 삼양로 188 5층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bum903</t>
+          <t>https://www.instagram.com/jjfit_7707</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4357,7 +4353,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4377,13 +4373,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="Q42" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4392,17 +4388,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>13162791</t>
+          <t>804545907</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13162791</t>
+          <t>https://m.place.naver.com/place/804545907</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4414,29 +4410,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>빌리프짐 수유점</t>
+          <t>노블휘트니스</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>beliefgym4@naver.com</t>
+          <t>noble_fitness@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1343-9679</t>
+          <t>0507-1421-2221</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
+          <t>서울특별시 강북구 한천로 1093 농협건물 2층 노블휘트니스</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beliefgym_suyu/</t>
+          <t>https://blog.naver.com/noble_fitness</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4451,7 +4447,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4471,13 +4467,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1621</v>
+        <v>175</v>
       </c>
       <c r="Q43" t="n">
-        <v>1197</v>
+        <v>130</v>
       </c>
       <c r="R43" t="n">
-        <v>2818</v>
+        <v>305</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4486,56 +4482,56 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1058492468</t>
+          <t>36246823</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058492468</t>
+          <t>https://m.place.naver.com/place/36246823</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>모티오나 재활운동 센터</t>
+          <t>에브리피티 소그룹 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>motiona_js8875@naver.com</t>
+          <t>rkdqnr7184@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1328-8875</t>
+          <t>0507-1336-7184</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 113 지하1층</t>
+          <t>서울특별시 강북구 오패산로 411 지층 전체</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/motiona_js8875</t>
+          <t>http://pf.kakao.com/_QERxeG</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4545,7 +4541,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4556,22 +4552,22 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>17</v>
+        <v>462</v>
       </c>
       <c r="Q44" t="n">
-        <v>13</v>
+        <v>795</v>
       </c>
       <c r="R44" t="n">
-        <v>30</v>
+        <v>1257</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4580,17 +4576,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2050145894</t>
+          <t>1172555749</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2050145894</t>
+          <t>https://m.place.naver.com/place/1172555749</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4602,29 +4598,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>머슬엑스짐</t>
+          <t>프리원핏 미아점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ask4554@naver.com</t>
+          <t>uckyfycmko336@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1370-4554</t>
+          <t>0507-1380-1962</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로 1127 지하 1층 머슬엑스짐</t>
+          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ask4554</t>
+          <t>https://www.instagram.com/freewantfit__mia/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4639,7 +4635,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4655,17 +4651,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="Q45" t="n">
-        <v>202</v>
+        <v>94</v>
       </c>
       <c r="R45" t="n">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4674,61 +4670,61 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1735126857</t>
+          <t>2037364243</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735126857</t>
+          <t>https://m.place.naver.com/place/2037364243</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>건축,토목</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>honeymusclegym@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>070-8024-0922</t>
+          <t>0507-1331-4021</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 도봉로 130 2층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@명희달려</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4749,17 +4745,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4768,17 +4764,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1356268668</t>
+          <t>1057899676</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1356268668</t>
+          <t>https://m.place.naver.com/place/1057899676</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4790,29 +4786,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>스포애니 수유역점</t>
+          <t>바디채널 광산사거리점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>spoany52@naver.com</t>
+          <t>bodyfit_@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1310-9628</t>
+          <t>0507-1359-6850</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 358 코스타타워 12층</t>
+          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany52</t>
+          <t>https://www.instagram.com/bodychannel_kwangsan/?hl=ko</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4827,7 +4823,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4847,13 +4843,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2755</v>
+        <v>101</v>
       </c>
       <c r="Q47" t="n">
-        <v>2356</v>
+        <v>320</v>
       </c>
       <c r="R47" t="n">
-        <v>5111</v>
+        <v>421</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4862,17 +4858,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1440007035</t>
+          <t>1089484623</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1440007035</t>
+          <t>https://m.place.naver.com/place/1089484623</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4884,29 +4880,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>프리원핏 미아점</t>
+          <t>빌리프짐 수유점</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>lhj0709_@naver.com</t>
+          <t>beliefgym4@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1380-1962</t>
+          <t>0507-1343-9679</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로 75 지하 1층</t>
+          <t>서울특별시 강북구 도봉로77길 6 수유 이테크밸리 오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/freewantfit__mia/</t>
+          <t>https://www.instagram.com/beliefgym_suyu/</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4941,13 +4937,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>75</v>
+        <v>1621</v>
       </c>
       <c r="Q48" t="n">
-        <v>94</v>
+        <v>1197</v>
       </c>
       <c r="R48" t="n">
-        <v>169</v>
+        <v>2818</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4956,34 +4952,34 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2037364243</t>
+          <t>1058492468</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037364243</t>
+          <t>https://m.place.naver.com/place/1058492468</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>포레스트PT짐</t>
+          <t>큐에이치필라테스&amp;PT더프리미엄 수유점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>forestgym24@naver.com</t>
+          <t>qh-03@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4991,12 +4987,12 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
+          <t>서울특별시 강북구 도봉로 358 2층 202호 큐에이치 필라테스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/forestgym24/223778254580</t>
+          <t>https://blog.naver.com/qh-03</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5022,22 +5018,22 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Q49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R49" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5046,42 +5042,46 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1008319723</t>
+          <t>1397546953</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008319723</t>
+          <t>https://m.place.naver.com/place/1397546953</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>근육케어 EMS 클럽</t>
+          <t>서울가설재BT비티아시바PT피티아시바파이프비계임대시공판매</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>juh1357@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>070-8075-1025</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔매로45길 30 1층</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5121,13 +5121,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="R50" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5136,51 +5136,51 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1284736783</t>
+          <t>1003986024</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284736783</t>
+          <t>https://m.place.naver.com/place/1003986024</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>에이블짐 수유점</t>
+          <t>모티오나 재활운동 센터</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ablegym33@naver.com</t>
+          <t>motiona_js8875@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1340-7281</t>
+          <t>0507-1328-8875</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
+          <t>서울특별시 강북구 노해로 113 지하1층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym33/223928936059</t>
+          <t>https://blog.naver.com/motiona_js8875</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>4553</v>
+        <v>17</v>
       </c>
       <c r="Q51" t="n">
-        <v>1195</v>
+        <v>13</v>
       </c>
       <c r="R51" t="n">
-        <v>5748</v>
+        <v>30</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5230,61 +5230,57 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1745960523</t>
+          <t>2050145894</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1745960523</t>
+          <t>https://m.place.naver.com/place/2050145894</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>건축,토목</t>
+          <t>체력단련,운동</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>피티아시바</t>
+          <t>DL 운동센터</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>unixgaseol7@naver.com</t>
+          <t>gunwigun_official@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>070-5255-1240</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 솔매로22가길 11 2층 201호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://litt.ly/d.l.trainer</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5300,22 +5296,22 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5324,51 +5320,51 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1012926496</t>
+          <t>1479834103</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1012926496</t>
+          <t>https://m.place.naver.com/place/1479834103</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>애드TOP</t>
+          <t>굿바디필라테스 EMS트레이닝PT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>deoj4628@naver.com</t>
+          <t>goodbodypila-emspt@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>070-8227-7372</t>
+          <t>0507-1402-2233</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 166</t>
+          <t>서울특별시 강북구 삼양로 293 2층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/goodbodypila-emspt</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5378,12 +5374,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5403,13 +5399,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="Q53" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="R53" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5418,51 +5414,51 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>30824060</t>
+          <t>1408311287</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/30824060</t>
+          <t>https://m.place.naver.com/place/1408311287</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>바디코드 필라테스&amp;PT 수유점</t>
+          <t>핏의공식</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>bodycode_suyu@naver.com</t>
+          <t>gymseungeun@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1491-5667</t>
+          <t>0507-1458-1884</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 351 3층</t>
+          <t>서울특별시 강북구 한천로131길 17 4층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodycode_suyu</t>
+          <t>https://www.instagram.com/gymseungeun/</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5477,7 +5473,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5497,13 +5493,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>397</v>
+        <v>29</v>
       </c>
       <c r="Q54" t="n">
-        <v>242</v>
+        <v>47</v>
       </c>
       <c r="R54" t="n">
-        <v>639</v>
+        <v>76</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5512,51 +5508,51 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1888853511</t>
+          <t>2024627135</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1888853511</t>
+          <t>https://m.place.naver.com/place/2024627135</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>바디채널 광산사거리점</t>
+          <t>크로스핏 알앤엘 수유</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>bodyfit_@naver.com</t>
+          <t>crossfitrnl_su@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1359-6850</t>
+          <t>0507-1382-4849</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 노해로 87 301호, 402호</t>
+          <t>서울특별시 강북구 덕릉로 76 B1</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodychannel_kwangsan/?hl=ko</t>
+          <t>https://smartstore.naver.com/runandlift</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5591,13 +5587,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>101</v>
+        <v>194</v>
       </c>
       <c r="Q55" t="n">
-        <v>320</v>
+        <v>501</v>
       </c>
       <c r="R55" t="n">
-        <v>421</v>
+        <v>695</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5606,17 +5602,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1089484623</t>
+          <t>31777480</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089484623</t>
+          <t>https://m.place.naver.com/place/31777480</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5628,29 +5624,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>파인드미짐 헬스&amp;PT 수유역점</t>
+          <t>에이블짐 수유점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>find_me_pt_studio@naver.com</t>
+          <t>ablegym33@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1478-5103</t>
+          <t>0507-1340-7281</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로144길 11 2층</t>
+          <t>서울특별시 강북구 도봉로 315 에피소드 838 지하 1층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/find_me_pt_studio</t>
+          <t>https://blog.naver.com/ablegym33/223928936059</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5676,7 +5672,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5685,13 +5681,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>226</v>
+        <v>4553</v>
       </c>
       <c r="Q56" t="n">
-        <v>421</v>
+        <v>1195</v>
       </c>
       <c r="R56" t="n">
-        <v>647</v>
+        <v>5748</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5700,55 +5696,51 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1116831923</t>
+          <t>1745960523</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1116831923</t>
+          <t>https://m.place.naver.com/place/1745960523</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>허니머슬짐 헬스PT&amp;필라테스 미아점</t>
+          <t>다이어트모드 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>honeymusclegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>myeonghui5402@gmail.com</t>
-        </is>
-      </c>
+          <t>dietmode-@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1331-4021</t>
+          <t>0507-1301-8244</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 130 2층</t>
+          <t>서울특별시 강북구 도봉로 350 5층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://youtube.com/@명희달려</t>
+          <t>https://blog.naver.com/dietmode-</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5763,7 +5755,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5779,17 +5771,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="Q57" t="n">
-        <v>91</v>
+        <v>211</v>
       </c>
       <c r="R57" t="n">
-        <v>177</v>
+        <v>310</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5798,51 +5790,51 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1057899676</t>
+          <t>37637672</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1057899676</t>
+          <t>https://m.place.naver.com/place/37637672</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>존버짐 미아뉴타운점</t>
+          <t>에너메카휘트니스 미아사거리점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jonbergym3@naver.com</t>
+          <t>nyh314@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1368-4511</t>
+          <t>0507-1320-7744</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
+          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jonbergym3</t>
+          <t>https://www.instagram.com/enermeca2/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5877,13 +5869,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>78</v>
+        <v>1339</v>
       </c>
       <c r="Q58" t="n">
-        <v>220</v>
+        <v>885</v>
       </c>
       <c r="R58" t="n">
-        <v>298</v>
+        <v>2224</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5892,47 +5884,51 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1293414126</t>
+          <t>1756863852</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1293414126</t>
+          <t>https://m.place.naver.com/place/1756863852</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>굿핏 PT&amp;필라테스 미아사거리점</t>
+          <t>엘투휘트니스 수유번동점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1369-2202</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 12 5층 굿핏 퍼스널트레이닝</t>
+          <t>서울특별시 강북구 월계로37길 129 3층 301호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodfit9008</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5942,12 +5938,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5963,17 +5959,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>248</v>
+        <v>10</v>
       </c>
       <c r="Q59" t="n">
-        <v>1343</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>1591</v>
+        <v>11</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5982,51 +5978,51 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1850055844</t>
+          <t>2045876824</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850055844</t>
+          <t>https://m.place.naver.com/place/2045876824</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>굿바디필라테스 EMS트레이닝PT</t>
+          <t>애드TOP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>goodbodypila-emspt@naver.com</t>
+          <t>deoj4628@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1402-2233</t>
+          <t>070-8227-7372</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 293 2층</t>
+          <t>서울특별시 강북구 도봉로 166</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodbodypila-emspt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6036,12 +6032,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6061,13 +6057,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6076,51 +6072,51 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1408311287</t>
+          <t>30824060</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1408311287</t>
+          <t>https://m.place.naver.com/place/30824060</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>데일리PT샵 미아본점</t>
+          <t>소울휘트니스</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>dailypt0926@naver.com</t>
+          <t>h9a1n94@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1362-0934</t>
+          <t>02-985-5553</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 98</t>
+          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dailypt0926</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6130,12 +6126,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6155,13 +6151,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="Q61" t="n">
-        <v>1304</v>
+        <v>335</v>
       </c>
       <c r="R61" t="n">
-        <v>1382</v>
+        <v>450</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6170,51 +6166,51 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1069239956</t>
+          <t>37240884</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069239956</t>
+          <t>https://m.place.naver.com/place/37240884</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>하이프핏, 수유PT샵</t>
+          <t>라이프플러스휘트니스 번동점</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>her__zz@naver.com</t>
+          <t>lifeplus1209@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1301-9491</t>
+          <t>0507-1362-4534</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로88가길 4 1층</t>
+          <t>서울특별시 강북구 오현로 194 지하1층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hypedobby</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6224,7 +6220,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6234,10 +6230,14 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w48ak4</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>X</t>
@@ -6249,13 +6249,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>43</v>
+        <v>697</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="R62" t="n">
-        <v>43</v>
+        <v>842</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6264,17 +6264,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2099905937</t>
+          <t>1877606346</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099905937</t>
+          <t>https://m.place.naver.com/place/1877606346</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6286,29 +6286,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>밀리언짐 수유점</t>
+          <t>휘트니스피플 우먼 수유역점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>milliongym-suyu@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1357-9092</t>
+          <t>02-990-3912</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 352 1동 지하1층 B101~B106호</t>
+          <t>서울특별시 강북구 도봉로 373 3, 4층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/milliongym-suyu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6318,20 +6318,24 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r5j3</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr">
         <is>
           <t>X</t>
@@ -6343,13 +6347,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>60</v>
+        <v>1722</v>
       </c>
       <c r="Q63" t="n">
-        <v>1</v>
+        <v>404</v>
       </c>
       <c r="R63" t="n">
-        <v>61</v>
+        <v>2126</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6358,17 +6362,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>2061019894</t>
+          <t>1985390755</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061019894</t>
+          <t>https://m.place.naver.com/place/1985390755</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6380,18 +6384,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>가설재비티아시바피티아시바파이프유로폼임대대여설치</t>
+          <t>서울가설재BT비티아시바PT피티아시바파이프비계임대시공판매</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>rodtmdu12@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>070-8069-0779</t>
+          <t>070-8075-1072</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -6440,10 +6444,10 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6452,51 +6456,51 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1752172206</t>
+          <t>1764669223</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1752172206</t>
+          <t>https://m.place.naver.com/place/1764669223</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>스타필라테스</t>
+          <t>존버짐 미아뉴타운점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>3007761@naver.com</t>
+          <t>jonbergym3@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1347-9979</t>
+          <t>0507-1368-4511</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로13길 13 3층 스타필라테스</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/3007761</t>
+          <t>https://www.instagram.com/jonbergym3</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6511,7 +6515,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6531,13 +6535,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="Q65" t="n">
-        <v>490</v>
+        <v>220</v>
       </c>
       <c r="R65" t="n">
-        <v>574</v>
+        <v>298</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6546,61 +6550,61 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1573837078</t>
+          <t>1293414126</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1573837078</t>
+          <t>https://m.place.naver.com/place/1293414126</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>수유 재활운동센터 라이프리턴</t>
+          <t>에스핏 휘트니스 수유점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>lifereturn_suyu@naver.com</t>
+          <t>kdhonepick@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1377-5126</t>
+          <t>0507-1393-8101</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 한천로131길 36 동국빌딩 4층</t>
+          <t>서울특별시 강북구 도봉로67길 18 3층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_ExmdAX</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6610,13 +6614,17 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4toem</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6625,13 +6633,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="Q66" t="n">
-        <v>56</v>
+        <v>243</v>
       </c>
       <c r="R66" t="n">
-        <v>78</v>
+        <v>359</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6640,17 +6648,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>2013060255</t>
+          <t>1185739926</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013060255</t>
+          <t>https://m.place.naver.com/place/1185739926</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6662,29 +6670,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>피트니스 베네핏 수유역점</t>
+          <t>더블플러스휘트니스클럽</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>baekyuri802@naver.com</t>
+          <t>osbum0224@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1351-2438</t>
+          <t>0507-1306-3451</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 82 제네스타워 4층</t>
+          <t>서울특별시 강북구 인수봉로 293 2층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/baekyuri802</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6694,12 +6702,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6715,17 +6723,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>623</v>
+        <v>7</v>
       </c>
       <c r="Q67" t="n">
-        <v>339</v>
+        <v>6</v>
       </c>
       <c r="R67" t="n">
-        <v>962</v>
+        <v>13</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6734,51 +6742,51 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1550724103</t>
+          <t>1035955167</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1550724103</t>
+          <t>https://m.place.naver.com/place/1035955167</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>올바른PT 삼양사거리점</t>
+          <t>범휘트니스  수유점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>olbareunpt4_@naver.com</t>
+          <t>ddt341@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1366-4502</t>
+          <t>0507-1409-0851</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 삼양로 166 2층</t>
+          <t>서울특별시 강북구 삼양로 293</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/olbareunpt4_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6788,12 +6796,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6809,17 +6817,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="Q68" t="n">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="R68" t="n">
-        <v>269</v>
+        <v>57</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6828,61 +6836,61 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1034422634</t>
+          <t>13162791</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034422634</t>
+          <t>https://m.place.naver.com/place/13162791</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>라이프빌딩짐 헬스&amp;PT 미아점</t>
+          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>lifebuildingmia@naver.com</t>
+          <t>uphoria6825@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1332-1672</t>
+          <t>0507-1334-6825</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 136 9층</t>
+          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://landing-mia-ebon.vercel.app/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6892,10 +6900,14 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w405s2</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>O</t>
@@ -6907,13 +6919,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>321</v>
+        <v>230</v>
       </c>
       <c r="Q69" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R69" t="n">
-        <v>903</v>
+        <v>814</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6922,51 +6934,51 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>36362933</t>
+          <t>1037773645</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36362933</t>
+          <t>https://m.place.naver.com/place/1037773645</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>소울휘트니스</t>
+          <t>디와이비퍼포먼스트레이닝</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>h9a1n94@naver.com</t>
+          <t>lhj0709_@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>02-985-5553</t>
+          <t>0507-1436-2922</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 오패산로30길 10 대지쇼핑프라자 4층</t>
+          <t>서울특별시 강북구 도봉로15길 11 지층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/h9a1n94</t>
+          <t>https://www.instagram.com/dyb_performance</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6981,7 +6993,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7001,14 +7013,14 @@
         </is>
       </c>
       <c r="P70" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>58</v>
+      </c>
+      <c r="R70" t="n">
         <v>115</v>
       </c>
-      <c r="Q70" t="n">
-        <v>335</v>
-      </c>
-      <c r="R70" t="n">
-        <v>450</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>X</t>
@@ -7016,17 +7028,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>37240884</t>
+          <t>1667051610</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37240884</t>
+          <t>https://m.place.naver.com/place/1667051610</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7038,39 +7050,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>에너메카 휘트니스 미아점</t>
+          <t>하이엔드짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>nyh314@naver.com</t>
+          <t>highend_fit@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1344-1650</t>
+          <t>0507-1417-2362</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 327 테마빌딩 2층</t>
+          <t>서울특별시 강북구 한천로 1035 지하1층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nyh314</t>
+          <t>https://highendgymsuyu-landing.vercel.app</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7080,10 +7092,14 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5v4ny</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr">
         <is>
           <t>X</t>
@@ -7091,17 +7107,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>334</v>
+        <v>1818</v>
       </c>
       <c r="Q71" t="n">
-        <v>365</v>
+        <v>1186</v>
       </c>
       <c r="R71" t="n">
-        <v>699</v>
+        <v>3004</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7110,51 +7126,51 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>37615690</t>
+          <t>1953510990</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37615690</t>
+          <t>https://m.place.naver.com/place/1953510990</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>에스핏 휘트니스 수유점</t>
+          <t>가설자재,비티아시바피티아시바,난간대파이프판매,임대설치</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>kdhonepick@naver.com</t>
+          <t>rodtmdu12@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1393-8101</t>
+          <t>070-8174-8741</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로67길 18 3층</t>
+          <t>서울특별시 강북구 수유동</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kdhonepick</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7164,7 +7180,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7185,17 +7201,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7204,17 +7220,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1185739926</t>
+          <t>1338034788</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185739926</t>
+          <t>https://m.place.naver.com/place/1338034788</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7226,29 +7242,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>블랙핏pt샵 미아사거리점</t>
+          <t>포레스트PT짐</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>blackfit123@naver.com</t>
+          <t>forestgym24@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>0507-1309-1030</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 월계로 43 5층 블랙핏</t>
+          <t>서울특별시 강북구 삼양로27길 80 두산위브트레지움 2단지 305동 상가 205호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blackfit123</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7258,12 +7270,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7279,17 +7291,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="Q73" t="n">
-        <v>375</v>
+        <v>7</v>
       </c>
       <c r="R73" t="n">
-        <v>521</v>
+        <v>28</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7298,46 +7310,46 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1105932712</t>
+          <t>1008319723</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105932712</t>
+          <t>https://m.place.naver.com/place/1008319723</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>건축,토목</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>가설자재비티아시바피티아시바발안전난간대판매임대설치</t>
+          <t>더 퍼스트짐</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>rodtmdu12@naver.com</t>
+          <t>ssdaw1234@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>070-8083-6616</t>
+          <t>0507-1353-7541</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유동</t>
+          <t>서울특별시 강북구 한천로131길 29 3층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7362,10 +7374,14 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w47wce</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>X</t>
@@ -7373,17 +7389,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7392,17 +7408,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1740427970</t>
+          <t>1176777711</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1740427970</t>
+          <t>https://m.place.naver.com/place/1176777711</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7452,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymchoi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7446,20 +7462,24 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43zk4</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr">
         <is>
           <t>X</t>
@@ -7496,7 +7516,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7508,30 +7528,38 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>드림유어바디 필라테스 미아점</t>
+          <t>필라테스 케밍 수유점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>popleedon@naver.com</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+          <t>keming_@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>kemingcompany@gmail.com</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1329-9609</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로15길 11 3,4층 (드림유어바디)</t>
+          <t>서울특별시 강북구 도봉로 322 3층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dyb_pilates/</t>
+          <t>https://pilateskeming.com/</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7541,7 +7569,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7561,13 +7589,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1264</v>
+        <v>312</v>
       </c>
       <c r="Q76" t="n">
-        <v>239</v>
+        <v>189</v>
       </c>
       <c r="R76" t="n">
-        <v>1503</v>
+        <v>501</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7576,17 +7604,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>11630404</t>
+          <t>1901646336</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11630404</t>
+          <t>https://m.place.naver.com/place/1901646336</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7598,39 +7626,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>더바른휘트니스 PT &amp; 헬스 미아점</t>
+          <t>올레이디짐 가오리점</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>osbum0224@naver.com</t>
+          <t>winnnig@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>02-986-2534</t>
+          <t>0507-1369-0010</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 177 3층 더바른휘트니스</t>
+          <t>서울특별시 강북구 삼양로 416 2층</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>http://www.thebarunfitness.com</t>
+          <t>https://allladygym.imweb.me/</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7640,10 +7668,14 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4lqb7</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr">
         <is>
           <t>X</t>
@@ -7655,13 +7687,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q77" t="n">
-        <v>104</v>
+        <v>165</v>
       </c>
       <c r="R77" t="n">
-        <v>184</v>
+        <v>244</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7670,17 +7702,17 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>38636716</t>
+          <t>1633562526</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38636716</t>
+          <t>https://m.place.naver.com/place/1633562526</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7703,13 +7735,13 @@
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>070-8069-0778</t>
+          <t>070-8069-0779</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 미아동</t>
+          <t>서울특별시 강북구 번동</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7764,78 +7796,78 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1022266242</t>
+          <t>1752172206</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1022266242</t>
+          <t>https://m.place.naver.com/place/1752172206</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>필라테스 케밍 수유점</t>
+          <t>플로리다휘트니스 삼양동점</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>keming_@naver.com</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>kemingcompany@gmail.com</t>
-        </is>
-      </c>
+          <t>sd670@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1329-9609</t>
+          <t>0507-1417-9917</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 322 3층</t>
+          <t>서울특별시 강북구 삼양로 161 4층 플로리다휘트니스</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://pilateskeming.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4jggy</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr">
         <is>
           <t>X</t>
@@ -7847,13 +7879,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>312</v>
+        <v>87</v>
       </c>
       <c r="Q79" t="n">
-        <v>189</v>
+        <v>236</v>
       </c>
       <c r="R79" t="n">
-        <v>501</v>
+        <v>323</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7862,17 +7894,17 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1901646336</t>
+          <t>33937785</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1901646336</t>
+          <t>https://m.place.naver.com/place/33937785</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7884,29 +7916,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>다이어트모드 휘트니스 수유점</t>
+          <t>레디포짐 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>dietmode-@naver.com</t>
+          <t>ready4gymsuyu@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1301-8244</t>
+          <t>0507-1430-3344</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 350 5층</t>
+          <t>서울특별시 강북구 도봉로 308 6층 레디포짐 수유점</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dietmode-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7916,20 +7948,24 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcs9wn</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr">
         <is>
           <t>X</t>
@@ -7937,17 +7973,17 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>99</v>
+        <v>1086</v>
       </c>
       <c r="Q80" t="n">
-        <v>211</v>
+        <v>879</v>
       </c>
       <c r="R80" t="n">
-        <v>310</v>
+        <v>1965</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7956,17 +7992,17 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>37637672</t>
+          <t>38648497</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37637672</t>
+          <t>https://m.place.naver.com/place/38648497</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7978,34 +8014,38 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>트렌디우먼휘트니스 미아사거리역점</t>
+          <t>짐박스피트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>trend_hd4@naver.com</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>02-988-3124</t>
+          <t>0507-1391-2161</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
+          <t>서울특별시 강북구 도봉로 52</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trend_hd4</t>
+          <t>https://gymboxx.com/onceinayear?gym=79</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8020,13 +8060,17 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -8035,13 +8079,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2270</v>
+        <v>1150</v>
       </c>
       <c r="Q81" t="n">
-        <v>1440</v>
+        <v>41</v>
       </c>
       <c r="R81" t="n">
-        <v>3710</v>
+        <v>1191</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8050,51 +8094,51 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1885902314</t>
+          <t>2099546838</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885902314</t>
+          <t>https://m.place.naver.com/place/2099546838</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>유포리아 헬스PT&amp;필라테스 미아점</t>
+          <t>프레스짐 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>uphoria6825@naver.com</t>
+          <t>pressgym@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1334-6825</t>
+          <t>0507-1344-9688</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로10길 73 지하1층, 4층</t>
+          <t>서울특별시 강북구 삼양로 162 지하1층 B01호, B02호, B03호, B04호</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uphoria_mia_1/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8104,7 +8148,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8114,13 +8158,17 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5i8bi</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -8129,13 +8177,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Q82" t="n">
-        <v>584</v>
+        <v>45</v>
       </c>
       <c r="R82" t="n">
-        <v>814</v>
+        <v>281</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8144,51 +8192,51 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1037773645</t>
+          <t>1695685266</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037773645</t>
+          <t>https://m.place.naver.com/place/1695685266</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>판타스틱짐 수유점 여성전용피트니스</t>
+          <t>바디코드 필라테스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>blueskirt0704@naver.com</t>
+          <t>bodycode_suyu@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1338-1501</t>
+          <t>0507-1491-5667</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 343 야산빌딩 4층</t>
+          <t>서울특별시 강북구 도봉로 351 3층</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blueskirt0704</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8198,23 +8246,27 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46lxu</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8223,13 +8275,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>142</v>
+        <v>397</v>
       </c>
       <c r="Q83" t="n">
-        <v>523</v>
+        <v>242</v>
       </c>
       <c r="R83" t="n">
-        <v>665</v>
+        <v>639</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8238,51 +8290,47 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1914282686</t>
+          <t>1888853511</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914282686</t>
+          <t>https://m.place.naver.com/place/1888853511</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>짐코사트 헬스&amp;PT 수유점</t>
+          <t>F45 수유</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>97_cosat@naver.com</t>
+          <t>f45_suyu@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>0507-1308-4535</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 수유로 81 3층</t>
+          <t>서울특별시 강북구 도봉로 323 7층</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/97_cosat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8292,23 +8340,27 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wy43x6v</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -8317,13 +8369,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="Q84" t="n">
         <v>162</v>
       </c>
       <c r="R84" t="n">
-        <v>186</v>
+        <v>253</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8332,17 +8384,17 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1604797933</t>
+          <t>1853806359</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604797933</t>
+          <t>https://m.place.naver.com/place/1853806359</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8406,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>the GoodFit</t>
+          <t>근육케어 EMS 클럽</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>goodfit9008@naver.com</t>
+          <t>juh1357@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -8367,12 +8419,12 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
+          <t>서울특별시 강북구 솔매로45길 30 1층</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodfit9008</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8382,12 +8434,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8403,17 +8455,17 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q85" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="R85" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8422,42 +8474,46 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1222324632</t>
+          <t>1284736783</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222324632</t>
+          <t>https://m.place.naver.com/place/1284736783</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>F45 수유</t>
+          <t>웰케어 PT&amp;재활트레이닝 솔샘점</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>f45_suyu@naver.com</t>
+          <t>wellcare093@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1404-1390</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 323 7층</t>
+          <t>서울특별시 강북구 삼양로27길 43 5층 503호</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8487,27 +8543,27 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wy43x6v</t>
+          <t>https://talk.naver.com/ct/w9cv7l2</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="Q86" t="n">
-        <v>162</v>
+        <v>55</v>
       </c>
       <c r="R86" t="n">
-        <v>253</v>
+        <v>64</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8516,46 +8572,46 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1853806359</t>
+          <t>2039688284</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853806359</t>
+          <t>https://m.place.naver.com/place/2039688284</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>건축,토목</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>크로스핏 알앤엘 수유</t>
+          <t>피티아시바</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>crossfitrnl_su@naver.com</t>
+          <t>unixgaseol7@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1382-4849</t>
+          <t>070-5255-1240</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 덕릉로 76 B1</t>
+          <t>서울특별시 강북구 미아동</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8580,14 +8636,10 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4zmep</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>X</t>
@@ -8595,17 +8647,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>695</v>
+        <v>0</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8614,17 +8666,17 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>31777480</t>
+          <t>1012926496</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31777480</t>
+          <t>https://m.place.naver.com/place/1012926496</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -8636,24 +8688,24 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>스포애니 삼양사거리점</t>
+          <t>트렌디우먼휘트니스 미아사거리역점</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>spoany87@naver.com</t>
+          <t>trend_hd4@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0507-1338-9618</t>
+          <t>02-988-3124</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 솔샘로 233 지하1층</t>
+          <t>서울특별시 강북구 도봉로 30 11층 1101, 1102호</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -8683,7 +8735,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sak0</t>
+          <t>https://talk.naver.com/ct/wcfi5my</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -8697,13 +8749,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1465</v>
+        <v>2275</v>
       </c>
       <c r="Q88" t="n">
-        <v>1729</v>
+        <v>1440</v>
       </c>
       <c r="R88" t="n">
-        <v>3194</v>
+        <v>3715</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8712,17 +8764,17 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1790576623</t>
+          <t>1885902314</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1790576623</t>
+          <t>https://m.place.naver.com/place/1885902314</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -8734,24 +8786,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>엑시스피티</t>
+          <t>DW 휘트니스 헬스&amp;PT 수유점</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>axis_pt@naver.com</t>
+          <t>dwgym1@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0507-1339-8603</t>
+          <t>0507-1370-7849</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로8길 33 2층</t>
+          <t>서울특별시 강북구 도봉로 328 5층 502호</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8781,12 +8833,12 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wwrhsu4</t>
+          <t>https://talk.naver.com/ct/w4e814</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -8795,13 +8847,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>25</v>
+        <v>2665</v>
       </c>
       <c r="Q89" t="n">
-        <v>46</v>
+        <v>4803</v>
       </c>
       <c r="R89" t="n">
-        <v>71</v>
+        <v>7468</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8810,17 +8862,17 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>2055534881</t>
+          <t>1284235115</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055534881</t>
+          <t>https://m.place.naver.com/place/1284235115</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -8832,29 +8884,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>이성현퍼스널트레이닝</t>
+          <t>the GoodFit</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>sunghyunle2@naver.com</t>
+          <t>goodfit9008@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>0507-1437-5900</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 숭인로 63-1 3층 이성현퍼스널트레이닝</t>
+          <t>서울특별시 강북구 도봉로 34-8 3층 더굿핏</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sunghyunle2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8864,7 +8912,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8874,10 +8922,14 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4jtey</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr">
         <is>
           <t>X</t>
@@ -8889,13 +8941,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="Q90" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="R90" t="n">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8904,46 +8956,46 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>35384521</t>
+          <t>1222324632</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35384521</t>
+          <t>https://m.place.naver.com/place/1222324632</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>에너메카휘트니스 미아사거리점</t>
+          <t>라이프빌딩PT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>nyh314@naver.com</t>
+          <t>life_building_@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1320-7744</t>
+          <t>0507-1404-1363</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 강북구 도봉로 34 트레지오빌딩 3층</t>
+          <t>서울특별시 강북구 오패산로 114 2층 라이프빌딩 PT 미아사거리점</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8968,14 +9020,10 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcha8q</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>X</t>
@@ -8987,13 +9035,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1339</v>
+        <v>532</v>
       </c>
       <c r="Q91" t="n">
-        <v>885</v>
+        <v>2236</v>
       </c>
       <c r="R91" t="n">
-        <v>2224</v>
+        <v>2768</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -9002,17 +9050,17 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1756863852</t>
+          <t>1906517072</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756863852</t>
+          <t>https://m.place.naver.com/place/1906517072</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
